--- a/4 курс/ФИТ/Равновесные модели FC №1.xlsx
+++ b/4 курс/ФИТ/Равновесные модели FC №1.xlsx
@@ -27,9 +27,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="91">
-  <si>
-    <t>Вариант 1</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="99">
+  <si>
+    <t>Вариант 3</t>
   </si>
   <si>
     <t>Период сглаживания = 3</t>
@@ -56,6 +56,9 @@
     <t>Спрос</t>
   </si>
   <si>
+    <t>Предложение</t>
+  </si>
+  <si>
     <t>Доход</t>
   </si>
   <si>
@@ -71,6 +74,9 @@
     <t>По доходу (Ô)</t>
   </si>
   <si>
+    <t>По предложению (s)</t>
+  </si>
+  <si>
     <t>ln(L)</t>
   </si>
   <si>
@@ -80,12 +86,18 @@
     <t>ln(Ô)</t>
   </si>
   <si>
+    <t>ln(s)</t>
+  </si>
+  <si>
     <t>ln^2(Ô)</t>
   </si>
   <si>
     <t>ln^2(L)</t>
   </si>
   <si>
+    <t>ln^2(s)</t>
+  </si>
+  <si>
     <t>ln(Ô)*ln(L)</t>
   </si>
   <si>
@@ -95,6 +107,15 @@
     <t>ln(Y)*ln(L)</t>
   </si>
   <si>
+    <t>ln(s)*ln(L)</t>
+  </si>
+  <si>
+    <t>ln(s)*ln(Ô)</t>
+  </si>
+  <si>
+    <t>ln(s)*ln(Y)</t>
+  </si>
+  <si>
     <t>1..3</t>
   </si>
   <si>
@@ -152,15 +173,18 @@
     <t>19..21</t>
   </si>
   <si>
+    <t>20..22</t>
+  </si>
+  <si>
+    <t>21..23</t>
+  </si>
+  <si>
+    <t>22..23</t>
+  </si>
+  <si>
     <t>Возьмём за X</t>
   </si>
   <si>
-    <t>N=</t>
-  </si>
-  <si>
-    <t>Месяцев</t>
-  </si>
-  <si>
     <t>x1 =</t>
   </si>
   <si>
@@ -263,31 +287,38 @@
     <t>Us</t>
   </si>
   <si>
+    <t>Б0</t>
+  </si>
+  <si>
+    <t>Предельная эффективность спроса по цене</t>
+  </si>
+  <si>
+    <t>Ud</t>
+  </si>
+  <si>
     <t>&gt;0</t>
   </si>
   <si>
-    <t>Предельная эффективность спроса по цене</t>
-  </si>
-  <si>
-    <t>Ud</t>
-  </si>
-  <si>
     <t>Предельная эффективность спроса по доходу</t>
   </si>
   <si>
     <t>β (эластичность по цене) =</t>
   </si>
   <si>
-    <t>При увеличении цены на 1% спрос повышается на 0.361%.</t>
+    <t>При увеличении цены на 1% спрос понижается на 1.613%.</t>
   </si>
   <si>
     <t>Так как |β| &lt; 1, спрос является неэластичным по цене.</t>
   </si>
   <si>
-    <t>Это товар первой необходимости — люди продолжат его покупать даже при росте цен, потому что заменить нечем.</t>
-  </si>
-  <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">Эластичность спроса </t>
     </r>
     <r>
@@ -323,7 +354,7 @@
     <t>α (эластичность по доходу) =</t>
   </si>
   <si>
-    <t>При увеличении дохода на 1% спросповышается на 1.009%.</t>
+    <t>При увеличении дохода на 1% спросповышается на 8.412%.</t>
   </si>
   <si>
     <t>Отрицательное значение означает, что товар относится к категории инфериорных (низкокачественных).</t>
@@ -378,14 +409,14 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
+      <sz val="11"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
@@ -760,7 +791,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="25">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -773,20 +804,7 @@
         <color rgb="FF000000"/>
       </left>
       <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -879,6 +897,32 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
@@ -892,6 +936,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
@@ -899,6 +963,47 @@
         <color rgb="FF000000"/>
       </right>
       <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -924,28 +1029,6 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1090,7 +1173,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1102,34 +1185,34 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1214,29 +1297,26 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="138">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1244,208 +1324,212 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="180" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -1455,64 +1539,41 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1850,7 +1911,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Равновесные модели FC №1'!$E$4</c:f>
+              <c:f>'Равновесные модели FC №1'!$F$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1876,10 +1937,10 @@
           </c:dLbls>
           <c:val>
             <c:numRef>
-              <c:f>'Равновесные модели FC №1'!$E$5:$E$27</c:f>
+              <c:f>'Равновесные модели FC №1'!$F$5:$F$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="23"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>25800</c:v>
                 </c:pt>
@@ -1940,6 +2001,15 @@
                 <c:pt idx="19">
                   <c:v>29000</c:v>
                 </c:pt>
+                <c:pt idx="20">
+                  <c:v>29000</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>32000</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>32000</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1950,7 +2020,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Равновесные модели FC №1'!$I$4</c:f>
+              <c:f>'Равновесные модели FC №1'!$J$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1976,10 +2046,10 @@
           </c:dLbls>
           <c:val>
             <c:numRef>
-              <c:f>'Равновесные модели FC №1'!$I$5:$I$27</c:f>
+              <c:f>'Равновесные модели FC №1'!$J$5:$J$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="23"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="1" c:formatCode="0.000">
                   <c:v>25891.6666666667</c:v>
                 </c:pt>
@@ -2036,6 +2106,15 @@
                 </c:pt>
                 <c:pt idx="19" c:formatCode="0.000">
                   <c:v>29000</c:v>
+                </c:pt>
+                <c:pt idx="20" c:formatCode="0.000">
+                  <c:v>30000</c:v>
+                </c:pt>
+                <c:pt idx="21" c:formatCode="0.000">
+                  <c:v>31000</c:v>
+                </c:pt>
+                <c:pt idx="22" c:formatCode="0.000">
+                  <c:v>32000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2261,7 +2340,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>638175</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="5715000" cy="3533775"/>
@@ -2271,7 +2350,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="638175" y="7105650"/>
+        <a:off x="638175" y="7858125"/>
         <a:ext cx="5715000" cy="3533775"/>
       </xdr:xfrm>
       <a:graphic>
@@ -2284,9 +2363,9 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>561975</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="8029575" cy="3248025"/>
@@ -2303,7 +2382,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18202275" y="6057900"/>
+          <a:off x="22393275" y="6810375"/>
           <a:ext cx="8029575" cy="3248025"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2318,7 +2397,7 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>1143000</xdr:colOff>
-      <xdr:row>111</xdr:row>
+      <xdr:row>114</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2076450" cy="581025"/>
@@ -2335,7 +2414,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5638800" y="22021800"/>
+          <a:off x="5638800" y="22774275"/>
           <a:ext cx="2076450" cy="581025"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2348,9 +2427,9 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>742950</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2076450" cy="581025"/>
@@ -2367,7 +2446,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12382500" y="5524500"/>
+          <a:off x="13677900" y="6276975"/>
           <a:ext cx="2076450" cy="581025"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2381,9 +2460,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="8725535" cy="273685"/>
     <xdr:sp>
@@ -2393,7 +2472,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="895350" y="4762500"/>
+          <a:off x="838200" y="5572125"/>
           <a:ext cx="8725535" cy="273685"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2434,7 +2513,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>180975</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="8172450" cy="273685"/>
@@ -2445,7 +2524,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="962025" y="5591175"/>
+          <a:off x="962025" y="6343650"/>
           <a:ext cx="8172450" cy="273685"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2486,7 +2565,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="11135995" cy="456565"/>
@@ -2497,7 +2576,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="781050" y="6543675"/>
+          <a:off x="781050" y="7296150"/>
           <a:ext cx="11135995" cy="456565"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2546,7 +2625,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>101</xdr:row>
+      <xdr:row>104</xdr:row>
       <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="8172450" cy="456565"/>
@@ -2557,7 +2636,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="781050" y="20097750"/>
+          <a:off x="781050" y="20850225"/>
           <a:ext cx="8172450" cy="456565"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2604,7 +2683,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>29210</xdr:colOff>
-      <xdr:row>108</xdr:row>
+      <xdr:row>111</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="11260455" cy="456565"/>
@@ -2615,7 +2694,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="686435" y="21564600"/>
+          <a:off x="686435" y="22317075"/>
           <a:ext cx="11260455" cy="456565"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2664,7 +2743,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>114</xdr:row>
+      <xdr:row>117</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="4134485" cy="273685"/>
@@ -2675,7 +2754,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="733425" y="22736175"/>
+          <a:off x="733425" y="23488650"/>
           <a:ext cx="4134485" cy="273685"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2716,7 +2795,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>123</xdr:row>
+      <xdr:row>126</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="5789930" cy="456565"/>
@@ -2727,7 +2806,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="24526875"/>
+          <a:off x="876300" y="25279350"/>
           <a:ext cx="5789930" cy="456565"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2776,7 +2855,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>143510</xdr:colOff>
-      <xdr:row>126</xdr:row>
+      <xdr:row>129</xdr:row>
       <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="5690870" cy="273685"/>
@@ -2787,7 +2866,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="800735" y="25098375"/>
+          <a:off x="800735" y="25850850"/>
           <a:ext cx="5690870" cy="273685"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2828,7 +2907,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>609600</xdr:colOff>
-      <xdr:row>142</xdr:row>
+      <xdr:row>145</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9880600" cy="639445"/>
@@ -2839,7 +2918,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="609600" y="28317825"/>
+          <a:off x="609600" y="29070300"/>
           <a:ext cx="9880600" cy="639445"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3097,1487 +3176,2352 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q1000"/>
+  <dimension ref="A1:X1003"/>
   <sheetFormatPr defaultColWidth="14.4285714285714" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.85714285714286" style="1" customWidth="1"/>
     <col min="2" max="2" width="27" style="1" customWidth="1"/>
     <col min="3" max="3" width="30.5714285714286" style="1" customWidth="1"/>
-    <col min="4" max="5" width="19.4285714285714" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.8571428571429" style="1" customWidth="1"/>
-    <col min="7" max="7" width="21.7142857142857" style="1" customWidth="1"/>
-    <col min="8" max="8" width="25.7142857142857" style="1" customWidth="1"/>
-    <col min="9" max="9" width="24.8571428571429" style="1" customWidth="1"/>
-    <col min="10" max="17" width="21.7142857142857" style="1" customWidth="1"/>
-    <col min="18" max="26" width="8.71428571428571" style="1" customWidth="1"/>
-    <col min="27" max="16384" width="14.4285714285714" style="1"/>
+    <col min="4" max="6" width="19.4285714285714" style="1" customWidth="1"/>
+    <col min="7" max="7" width="20.8571428571429" style="1" customWidth="1"/>
+    <col min="8" max="8" width="21.7142857142857" style="1" customWidth="1"/>
+    <col min="9" max="9" width="25.7142857142857" style="1" customWidth="1"/>
+    <col min="10" max="10" width="24.8571428571429" style="1" customWidth="1"/>
+    <col min="11" max="21" width="21.7142857142857" style="1" customWidth="1"/>
+    <col min="22" max="22" width="19" style="1" customWidth="1"/>
+    <col min="23" max="23" width="13.7142857142857" style="1" customWidth="1"/>
+    <col min="24" max="24" width="15.0952380952381" style="1" customWidth="1"/>
+    <col min="25" max="30" width="8.71428571428571" style="1" customWidth="1"/>
+    <col min="31" max="16384" width="14.4285714285714" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:2">
+    <row r="1" spans="2:21">
       <c r="B1" s="2"/>
-    </row>
-    <row r="2" spans="2:17">
-      <c r="B2" s="3" t="s">
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+    </row>
+    <row r="2" ht="27" spans="2:21">
+      <c r="B2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="5" t="s">
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="56">
+      <c r="I2" s="3"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="41"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="41">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:17">
-      <c r="B3" s="4"/>
-      <c r="C3" s="6" t="s">
+    <row r="3" spans="2:21">
+      <c r="B3" s="3"/>
+      <c r="C3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="2"/>
+      <c r="F3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="3"/>
+      <c r="H3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="8"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="58"/>
-    </row>
-    <row r="4" spans="2:17">
-      <c r="B4" s="9" t="s">
+      <c r="I3" s="42"/>
+      <c r="J3" s="42"/>
+      <c r="K3" s="43"/>
+      <c r="L3" s="44"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="44"/>
+    </row>
+    <row r="4" spans="2:24">
+      <c r="B4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="L4" s="11" t="s">
+      <c r="L4" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="M4" s="11" t="s">
+      <c r="M4" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N4" s="11" t="s">
+      <c r="N4" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="O4" s="11" t="s">
+      <c r="O4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="P4" s="11" t="s">
+      <c r="P4" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="Q4" s="11" t="s">
+      <c r="Q4" s="9" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="5" spans="2:17">
-      <c r="B5" s="12">
+      <c r="R4" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="S4" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="T4" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="U4" s="56" t="s">
+        <v>25</v>
+      </c>
+      <c r="V4" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="W4" s="45" t="s">
+        <v>27</v>
+      </c>
+      <c r="X4" s="45" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="2:24">
+      <c r="B5" s="7">
         <v>1</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="7">
         <v>270</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="7">
         <v>97950</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="10">
+        <v>144000</v>
+      </c>
+      <c r="F5" s="11">
         <v>25800</v>
       </c>
-      <c r="F5" s="10"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="14"/>
-      <c r="K5" s="14"/>
-      <c r="L5" s="14"/>
-      <c r="M5" s="14"/>
-      <c r="N5" s="14"/>
-      <c r="O5" s="14"/>
-      <c r="P5" s="14"/>
-      <c r="Q5" s="14"/>
-    </row>
-    <row r="6" spans="2:17">
-      <c r="B6" s="12">
+      <c r="G5" s="8"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="9"/>
+      <c r="U5" s="56"/>
+      <c r="V5" s="45"/>
+      <c r="W5" s="45"/>
+      <c r="X5" s="45"/>
+    </row>
+    <row r="6" spans="2:24">
+      <c r="B6" s="7">
         <v>2</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="7">
         <v>270</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="7">
         <v>98350</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="10">
+        <v>157600</v>
+      </c>
+      <c r="F6" s="11">
         <v>25875</v>
       </c>
-      <c r="F6" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="15">
-        <f t="shared" ref="G6:I6" si="0">AVERAGE(C5:C7)</f>
+      <c r="G6" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="12">
+        <f>AVERAGE(C5:C7)</f>
         <v>260</v>
       </c>
-      <c r="H6" s="15">
-        <f t="shared" si="0"/>
+      <c r="I6" s="12">
+        <f>AVERAGE(D5:D7)</f>
         <v>104200</v>
       </c>
-      <c r="I6" s="15">
-        <f t="shared" si="0"/>
+      <c r="J6" s="12">
+        <f>AVERAGE(F5:F7)</f>
         <v>25891.6666666667</v>
       </c>
-      <c r="J6" s="15">
-        <f t="shared" ref="J6:L6" si="1">LN(G6)</f>
+      <c r="K6" s="45">
+        <f>AVERAGE(E5:E7)</f>
+        <v>170560</v>
+      </c>
+      <c r="L6" s="12">
+        <f>LN(H6)</f>
         <v>5.56068163101553</v>
       </c>
-      <c r="K6" s="15">
+      <c r="M6" s="12">
+        <f t="shared" ref="L6:N6" si="0">LN(I6)</f>
+        <v>11.5540674083014</v>
+      </c>
+      <c r="N6" s="46">
+        <f>LN(J6)</f>
+        <v>10.1616764455931</v>
+      </c>
+      <c r="O6" s="47">
+        <f>LN(K6)</f>
+        <v>12.0468424199596</v>
+      </c>
+      <c r="P6" s="48">
+        <f>N6*N6</f>
+        <v>103.259668184922</v>
+      </c>
+      <c r="Q6" s="12">
+        <f t="shared" ref="Q6:Q27" si="1">L6*L6</f>
+        <v>30.9211802015135</v>
+      </c>
+      <c r="R6" s="12">
+        <f>O6*O6</f>
+        <v>145.126412291339</v>
+      </c>
+      <c r="S6" s="12">
+        <f t="shared" ref="S6:S27" si="2">N6*L6</f>
+        <v>56.5058475513329</v>
+      </c>
+      <c r="T6" s="12">
+        <f t="shared" ref="T6:T27" si="3">M6*N6</f>
+        <v>117.408694633732</v>
+      </c>
+      <c r="U6" s="46">
+        <f t="shared" ref="U6:U27" si="4">M6*L6</f>
+        <v>64.2484904008568</v>
+      </c>
+      <c r="V6" s="57">
+        <f>O6*L6</f>
+        <v>66.9886553564081</v>
+      </c>
+      <c r="W6" s="57">
+        <f>M6*O6</f>
+        <v>139.190029377398</v>
+      </c>
+      <c r="X6" s="57">
+        <f>O6*N6</f>
+        <v>122.416114862676</v>
+      </c>
+    </row>
+    <row r="7" spans="2:24">
+      <c r="B7" s="7">
+        <v>3</v>
+      </c>
+      <c r="C7" s="7">
+        <v>240</v>
+      </c>
+      <c r="D7" s="11">
+        <v>116300</v>
+      </c>
+      <c r="E7" s="10">
+        <v>210080</v>
+      </c>
+      <c r="F7" s="11">
+        <v>26000</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" s="12">
+        <f>AVERAGE(C6:C8)</f>
+        <v>250</v>
+      </c>
+      <c r="I7" s="12">
+        <f>AVERAGE(D6:D8)</f>
+        <v>110323.333333333</v>
+      </c>
+      <c r="J7" s="12">
+        <f>AVERAGE(F6:F8)</f>
+        <v>25958.3333333333</v>
+      </c>
+      <c r="K7" s="45">
+        <f t="shared" ref="K7:K27" si="5">AVERAGE(E6:E8)</f>
+        <v>195870</v>
+      </c>
+      <c r="L7" s="12">
+        <f>LN(H7)</f>
+        <v>5.52146091786225</v>
+      </c>
+      <c r="M7" s="12">
+        <f t="shared" ref="L7:N7" si="6">LN(I7)</f>
+        <v>11.6111707271425</v>
+      </c>
+      <c r="N7" s="46">
+        <f t="shared" si="6"/>
+        <v>10.1642479674216</v>
+      </c>
+      <c r="O7" s="47">
+        <f t="shared" ref="O7:O27" si="7">LN(K7)</f>
+        <v>12.1852064528488</v>
+      </c>
+      <c r="P7" s="48">
+        <f t="shared" ref="P6:P27" si="8">N7*N7</f>
+        <v>103.311936743235</v>
+      </c>
+      <c r="Q7" s="12">
         <f t="shared" si="1"/>
-        <v>11.5540674083014</v>
-      </c>
-      <c r="L6" s="15">
+        <v>30.4865306674802</v>
+      </c>
+      <c r="R7" s="12">
+        <f t="shared" ref="R7:R27" si="9">O7*O7</f>
+        <v>148.479256298548</v>
+      </c>
+      <c r="S7" s="12">
+        <f t="shared" si="2"/>
+        <v>56.1214979115794</v>
+      </c>
+      <c r="T7" s="12">
+        <f t="shared" si="3"/>
+        <v>118.018818462743</v>
+      </c>
+      <c r="U7" s="46">
+        <f t="shared" si="4"/>
+        <v>64.1106253805432</v>
+      </c>
+      <c r="V7" s="57">
+        <f t="shared" ref="V7:V27" si="10">O7*L7</f>
+        <v>67.2801412054874</v>
+      </c>
+      <c r="W7" s="57">
+        <f t="shared" ref="W7:W27" si="11">M7*O7</f>
+        <v>141.484512469505</v>
+      </c>
+      <c r="X7" s="57">
+        <f t="shared" ref="X7:X27" si="12">O7*N7</f>
+        <v>123.853459920981</v>
+      </c>
+    </row>
+    <row r="8" spans="2:24">
+      <c r="B8" s="7">
+        <v>4</v>
+      </c>
+      <c r="C8" s="7">
+        <v>240</v>
+      </c>
+      <c r="D8" s="11">
+        <v>116320</v>
+      </c>
+      <c r="E8" s="10">
+        <v>219930</v>
+      </c>
+      <c r="F8" s="11">
+        <v>26000</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8" s="12">
+        <f>AVERAGE(C7:C9)</f>
+        <v>259.333333333333</v>
+      </c>
+      <c r="I8" s="12">
+        <f>AVERAGE(D7:D9)</f>
+        <v>138140</v>
+      </c>
+      <c r="J8" s="12">
+        <f>AVERAGE(F7:F9)</f>
+        <v>26133.3333333333</v>
+      </c>
+      <c r="K8" s="45">
+        <f t="shared" si="5"/>
+        <v>231670</v>
+      </c>
+      <c r="L8" s="12">
+        <f t="shared" ref="L8:N8" si="13">LN(H8)</f>
+        <v>5.55811423551028</v>
+      </c>
+      <c r="M8" s="12">
+        <f t="shared" si="13"/>
+        <v>11.836022942643</v>
+      </c>
+      <c r="N8" s="46">
+        <f t="shared" si="13"/>
+        <v>10.1709669176704</v>
+      </c>
+      <c r="O8" s="47">
+        <f t="shared" si="7"/>
+        <v>12.3530692242645</v>
+      </c>
+      <c r="P8" s="48">
+        <f t="shared" si="8"/>
+        <v>103.448568040346</v>
+      </c>
+      <c r="Q8" s="12">
         <f t="shared" si="1"/>
-        <v>10.1616764455931</v>
-      </c>
-      <c r="M6" s="15">
-        <f t="shared" ref="M6:M27" si="2">L6*L6</f>
-        <v>103.259668184922</v>
-      </c>
-      <c r="N6" s="15">
-        <f t="shared" ref="N6:N27" si="3">J6*J6</f>
-        <v>30.9211802015135</v>
-      </c>
-      <c r="O6" s="15">
-        <f t="shared" ref="O6:O27" si="4">L6*J6</f>
-        <v>56.5058475513329</v>
-      </c>
-      <c r="P6" s="15">
-        <f t="shared" ref="P6:P27" si="5">K6*L6</f>
-        <v>117.408694633732</v>
-      </c>
-      <c r="Q6" s="15">
-        <f t="shared" ref="Q6:Q27" si="6">K6*J6</f>
-        <v>64.2484904008568</v>
-      </c>
-    </row>
-    <row r="7" spans="2:17">
-      <c r="B7" s="12">
-        <v>3</v>
-      </c>
-      <c r="C7" s="12">
-        <v>240</v>
-      </c>
-      <c r="D7" s="13">
-        <v>116300</v>
-      </c>
-      <c r="E7" s="13">
-        <v>26000</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" s="15">
-        <f t="shared" ref="G7:I7" si="7">AVERAGE(C6:C8)</f>
-        <v>250</v>
-      </c>
-      <c r="H7" s="15">
+        <v>30.892633854982</v>
+      </c>
+      <c r="R8" s="12">
+        <f t="shared" si="9"/>
+        <v>152.598319259471</v>
+      </c>
+      <c r="S8" s="12">
+        <f t="shared" si="2"/>
+        <v>56.5313960140079</v>
+      </c>
+      <c r="T8" s="12">
+        <f t="shared" si="3"/>
+        <v>120.383797786409</v>
+      </c>
+      <c r="U8" s="46">
+        <f t="shared" si="4"/>
+        <v>65.7859676093302</v>
+      </c>
+      <c r="V8" s="57">
+        <f t="shared" si="10"/>
+        <v>68.6597699076286</v>
+      </c>
+      <c r="W8" s="57">
+        <f t="shared" si="11"/>
+        <v>146.211210750452</v>
+      </c>
+      <c r="X8" s="57">
+        <f t="shared" si="12"/>
+        <v>125.642658411687</v>
+      </c>
+    </row>
+    <row r="9" spans="2:24">
+      <c r="B9" s="7">
+        <v>5</v>
+      </c>
+      <c r="C9" s="7">
+        <v>298</v>
+      </c>
+      <c r="D9" s="11">
+        <v>181800</v>
+      </c>
+      <c r="E9" s="10">
+        <v>265000</v>
+      </c>
+      <c r="F9" s="11">
+        <v>26400</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9" s="12">
+        <f>AVERAGE(C8:C10)</f>
+        <v>266</v>
+      </c>
+      <c r="I9" s="12">
+        <f>AVERAGE(D8:D10)</f>
+        <v>173040</v>
+      </c>
+      <c r="J9" s="12">
+        <f>AVERAGE(F8:F10)</f>
+        <v>26533.3333333333</v>
+      </c>
+      <c r="K9" s="45">
+        <f t="shared" si="5"/>
+        <v>250573.333333333</v>
+      </c>
+      <c r="L9" s="12">
+        <f t="shared" ref="L9:N9" si="14">LN(H9)</f>
+        <v>5.5834963087817</v>
+      </c>
+      <c r="M9" s="12">
+        <f t="shared" si="14"/>
+        <v>12.0612780606269</v>
+      </c>
+      <c r="N9" s="46">
+        <f t="shared" si="14"/>
+        <v>10.1861570831644</v>
+      </c>
+      <c r="O9" s="47">
         <f t="shared" si="7"/>
-        <v>110323.333333333</v>
-      </c>
-      <c r="I7" s="15">
+        <v>12.4315069045024</v>
+      </c>
+      <c r="P9" s="48">
+        <f t="shared" si="8"/>
+        <v>103.7577961229</v>
+      </c>
+      <c r="Q9" s="12">
+        <f t="shared" si="1"/>
+        <v>31.1754310301789</v>
+      </c>
+      <c r="R9" s="12">
+        <f t="shared" si="9"/>
+        <v>154.542363916692</v>
+      </c>
+      <c r="S9" s="12">
+        <f t="shared" si="2"/>
+        <v>56.8743704745188</v>
+      </c>
+      <c r="T9" s="12">
+        <f t="shared" si="3"/>
+        <v>122.85807294927</v>
+      </c>
+      <c r="U9" s="46">
+        <f t="shared" si="4"/>
+        <v>67.3441015307002</v>
+      </c>
+      <c r="V9" s="57">
+        <f t="shared" si="10"/>
+        <v>69.4112729138835</v>
+      </c>
+      <c r="W9" s="57">
+        <f t="shared" si="11"/>
+        <v>149.939861487807</v>
+      </c>
+      <c r="X9" s="57">
+        <f t="shared" si="12"/>
+        <v>126.629282109704</v>
+      </c>
+    </row>
+    <row r="10" spans="2:24">
+      <c r="B10" s="7">
+        <v>6</v>
+      </c>
+      <c r="C10" s="7">
+        <v>260</v>
+      </c>
+      <c r="D10" s="11">
+        <v>221000</v>
+      </c>
+      <c r="E10" s="10">
+        <v>266790</v>
+      </c>
+      <c r="F10" s="11">
+        <v>27200</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="H10" s="12">
+        <f>AVERAGE(C9:C11)</f>
+        <v>272.666666666667</v>
+      </c>
+      <c r="I10" s="12">
+        <f>AVERAGE(D9:D11)</f>
+        <v>226283.333333333</v>
+      </c>
+      <c r="J10" s="12">
+        <f>AVERAGE(F9:F11)</f>
+        <v>26950</v>
+      </c>
+      <c r="K10" s="45">
+        <f t="shared" si="5"/>
+        <v>268563.333333333</v>
+      </c>
+      <c r="L10" s="12">
+        <f t="shared" ref="L10:N10" si="15">LN(H10)</f>
+        <v>5.60825004793464</v>
+      </c>
+      <c r="M10" s="12">
+        <f t="shared" si="15"/>
+        <v>12.3295431803603</v>
+      </c>
+      <c r="N10" s="46">
+        <f t="shared" si="15"/>
+        <v>10.2017385763371</v>
+      </c>
+      <c r="O10" s="47">
         <f t="shared" si="7"/>
-        <v>25958.3333333333</v>
-      </c>
-      <c r="J7" s="15">
-        <f t="shared" ref="J7:L7" si="8">LN(G7)</f>
-        <v>5.52146091786225</v>
-      </c>
-      <c r="K7" s="15">
+        <v>12.5008420434526</v>
+      </c>
+      <c r="P10" s="48">
         <f t="shared" si="8"/>
-        <v>11.6111707271425</v>
-      </c>
-      <c r="L7" s="15">
-        <f t="shared" si="8"/>
-        <v>10.1642479674216</v>
-      </c>
-      <c r="M7" s="15">
+        <v>104.075469979925</v>
+      </c>
+      <c r="Q10" s="12">
+        <f t="shared" si="1"/>
+        <v>31.4524686001589</v>
+      </c>
+      <c r="R10" s="12">
+        <f t="shared" si="9"/>
+        <v>156.271051795351</v>
+      </c>
+      <c r="S10" s="12">
         <f t="shared" si="2"/>
-        <v>103.311936743235</v>
-      </c>
-      <c r="N7" s="15">
+        <v>57.2139008597594</v>
+      </c>
+      <c r="T10" s="12">
         <f t="shared" si="3"/>
-        <v>30.4865306674802</v>
-      </c>
-      <c r="O7" s="15">
+        <v>125.782776291696</v>
+      </c>
+      <c r="U10" s="46">
         <f t="shared" si="4"/>
-        <v>56.1214979115794</v>
-      </c>
-      <c r="P7" s="15">
+        <v>69.1471611322679</v>
+      </c>
+      <c r="V10" s="57">
+        <f t="shared" si="10"/>
+        <v>70.1078479894162</v>
+      </c>
+      <c r="W10" s="57">
+        <f t="shared" si="11"/>
+        <v>154.129671765612</v>
+      </c>
+      <c r="X10" s="57">
+        <f t="shared" si="12"/>
+        <v>127.530322511387</v>
+      </c>
+    </row>
+    <row r="11" spans="2:24">
+      <c r="B11" s="7">
+        <v>7</v>
+      </c>
+      <c r="C11" s="7">
+        <v>260</v>
+      </c>
+      <c r="D11" s="11">
+        <v>276050</v>
+      </c>
+      <c r="E11" s="10">
+        <v>273900</v>
+      </c>
+      <c r="F11" s="11">
+        <v>27250</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="H11" s="12">
+        <f>AVERAGE(C10:C12)</f>
+        <v>260</v>
+      </c>
+      <c r="I11" s="12">
+        <f>AVERAGE(D10:D12)</f>
+        <v>262560</v>
+      </c>
+      <c r="J11" s="12">
+        <f>AVERAGE(F10:F12)</f>
+        <v>27241.6666666667</v>
+      </c>
+      <c r="K11" s="45">
         <f t="shared" si="5"/>
-        <v>118.018818462743</v>
-      </c>
-      <c r="Q7" s="15">
-        <f t="shared" si="6"/>
-        <v>64.1106253805432</v>
-      </c>
-    </row>
-    <row r="8" spans="2:17">
-      <c r="B8" s="12">
-        <v>4</v>
-      </c>
-      <c r="C8" s="12">
-        <v>240</v>
-      </c>
-      <c r="D8" s="13">
-        <v>116320</v>
-      </c>
-      <c r="E8" s="13">
-        <v>26000</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="G8" s="15">
-        <f t="shared" ref="G8:I8" si="9">AVERAGE(C7:C9)</f>
-        <v>259.333333333333</v>
-      </c>
-      <c r="H8" s="15">
-        <f t="shared" si="9"/>
-        <v>138140</v>
-      </c>
-      <c r="I8" s="15">
-        <f t="shared" si="9"/>
-        <v>26133.3333333333</v>
-      </c>
-      <c r="J8" s="15">
-        <f t="shared" ref="J8:L8" si="10">LN(G8)</f>
-        <v>5.55811423551028</v>
-      </c>
-      <c r="K8" s="15">
-        <f t="shared" si="10"/>
-        <v>11.836022942643</v>
-      </c>
-      <c r="L8" s="15">
-        <f t="shared" si="10"/>
-        <v>10.1709669176704</v>
-      </c>
-      <c r="M8" s="15">
-        <f t="shared" si="2"/>
-        <v>103.448568040346</v>
-      </c>
-      <c r="N8" s="15">
-        <f t="shared" si="3"/>
-        <v>30.892633854982</v>
-      </c>
-      <c r="O8" s="15">
-        <f t="shared" si="4"/>
-        <v>56.5313960140079</v>
-      </c>
-      <c r="P8" s="15">
-        <f t="shared" si="5"/>
-        <v>120.383797786409</v>
-      </c>
-      <c r="Q8" s="15">
-        <f t="shared" si="6"/>
-        <v>65.7859676093302</v>
-      </c>
-    </row>
-    <row r="9" spans="2:17">
-      <c r="B9" s="12">
-        <v>5</v>
-      </c>
-      <c r="C9" s="12">
-        <v>298</v>
-      </c>
-      <c r="D9" s="13">
-        <v>181800</v>
-      </c>
-      <c r="E9" s="13">
-        <v>26400</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G9" s="15">
-        <f t="shared" ref="G9:I9" si="11">AVERAGE(C8:C10)</f>
-        <v>266</v>
-      </c>
-      <c r="H9" s="15">
-        <f t="shared" si="11"/>
-        <v>173040</v>
-      </c>
-      <c r="I9" s="15">
-        <f t="shared" si="11"/>
-        <v>26533.3333333333</v>
-      </c>
-      <c r="J9" s="15">
-        <f t="shared" ref="J9:L9" si="12">LN(G9)</f>
-        <v>5.5834963087817</v>
-      </c>
-      <c r="K9" s="15">
-        <f t="shared" si="12"/>
-        <v>12.0612780606269</v>
-      </c>
-      <c r="L9" s="15">
-        <f t="shared" si="12"/>
-        <v>10.1861570831644</v>
-      </c>
-      <c r="M9" s="15">
-        <f t="shared" si="2"/>
-        <v>103.7577961229</v>
-      </c>
-      <c r="N9" s="15">
-        <f t="shared" si="3"/>
-        <v>31.1754310301789</v>
-      </c>
-      <c r="O9" s="15">
-        <f t="shared" si="4"/>
-        <v>56.8743704745188</v>
-      </c>
-      <c r="P9" s="15">
-        <f t="shared" si="5"/>
-        <v>122.85807294927</v>
-      </c>
-      <c r="Q9" s="15">
-        <f t="shared" si="6"/>
-        <v>67.3441015307002</v>
-      </c>
-    </row>
-    <row r="10" spans="2:17">
-      <c r="B10" s="12">
-        <v>6</v>
-      </c>
-      <c r="C10" s="12">
-        <v>260</v>
-      </c>
-      <c r="D10" s="13">
-        <v>221000</v>
-      </c>
-      <c r="E10" s="13">
-        <v>27200</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" s="15">
-        <f t="shared" ref="G10:I10" si="13">AVERAGE(C9:C11)</f>
-        <v>272.666666666667</v>
-      </c>
-      <c r="H10" s="15">
-        <f t="shared" si="13"/>
-        <v>226283.333333333</v>
-      </c>
-      <c r="I10" s="15">
-        <f t="shared" si="13"/>
-        <v>26950</v>
-      </c>
-      <c r="J10" s="15">
-        <f t="shared" ref="J10:L10" si="14">LN(G10)</f>
-        <v>5.60825004793464</v>
-      </c>
-      <c r="K10" s="15">
-        <f t="shared" si="14"/>
-        <v>12.3295431803603</v>
-      </c>
-      <c r="L10" s="15">
-        <f t="shared" si="14"/>
-        <v>10.2017385763371</v>
-      </c>
-      <c r="M10" s="15">
-        <f t="shared" si="2"/>
-        <v>104.075469979925</v>
-      </c>
-      <c r="N10" s="15">
-        <f t="shared" si="3"/>
-        <v>31.4524686001589</v>
-      </c>
-      <c r="O10" s="15">
-        <f t="shared" si="4"/>
-        <v>57.2139008597594</v>
-      </c>
-      <c r="P10" s="15">
-        <f t="shared" si="5"/>
-        <v>125.782776291696</v>
-      </c>
-      <c r="Q10" s="15">
-        <f t="shared" si="6"/>
-        <v>69.1471611322679</v>
-      </c>
-    </row>
-    <row r="11" spans="2:17">
-      <c r="B11" s="12">
-        <v>7</v>
-      </c>
-      <c r="C11" s="12">
-        <v>260</v>
-      </c>
-      <c r="D11" s="13">
-        <v>276050</v>
-      </c>
-      <c r="E11" s="13">
-        <v>27250</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="G11" s="15">
-        <f t="shared" ref="G11:I11" si="15">AVERAGE(C10:C12)</f>
-        <v>260</v>
-      </c>
-      <c r="H11" s="15">
-        <f t="shared" si="15"/>
-        <v>262560</v>
-      </c>
-      <c r="I11" s="15">
-        <f t="shared" si="15"/>
-        <v>27241.6666666667</v>
-      </c>
-      <c r="J11" s="15">
-        <f t="shared" ref="J11:L11" si="16">LN(G11)</f>
+        <v>271530</v>
+      </c>
+      <c r="L11" s="12">
+        <f t="shared" ref="L11:N11" si="16">LN(H11)</f>
         <v>5.56068163101553</v>
       </c>
-      <c r="K11" s="15">
+      <c r="M11" s="12">
         <f t="shared" si="16"/>
         <v>12.4782349063239</v>
       </c>
-      <c r="L11" s="15">
+      <c r="N11" s="46">
         <f t="shared" si="16"/>
         <v>10.2125029429243</v>
       </c>
-      <c r="M11" s="15">
+      <c r="O11" s="47">
+        <f t="shared" si="7"/>
+        <v>12.5118279094893</v>
+      </c>
+      <c r="P11" s="48">
+        <f t="shared" si="8"/>
+        <v>104.295216359238</v>
+      </c>
+      <c r="Q11" s="12">
+        <f t="shared" si="1"/>
+        <v>30.9211802015135</v>
+      </c>
+      <c r="R11" s="12">
+        <f t="shared" si="9"/>
+        <v>156.545837636676</v>
+      </c>
+      <c r="S11" s="12">
         <f t="shared" si="2"/>
-        <v>104.295216359238</v>
-      </c>
-      <c r="N11" s="15">
+        <v>56.7884775214112</v>
+      </c>
+      <c r="T11" s="12">
         <f t="shared" si="3"/>
-        <v>30.9211802015135</v>
-      </c>
-      <c r="O11" s="15">
+        <v>127.434010703334</v>
+      </c>
+      <c r="U11" s="46">
         <f t="shared" si="4"/>
-        <v>56.7884775214112</v>
-      </c>
-      <c r="P11" s="15">
+        <v>69.3874916310922</v>
+      </c>
+      <c r="V11" s="57">
+        <f t="shared" si="10"/>
+        <v>69.5742916267247</v>
+      </c>
+      <c r="W11" s="57">
+        <f t="shared" si="11"/>
+        <v>156.125527762108</v>
+      </c>
+      <c r="X11" s="57">
+        <f t="shared" si="12"/>
+        <v>127.777079347022</v>
+      </c>
+    </row>
+    <row r="12" spans="2:24">
+      <c r="B12" s="7">
+        <v>8</v>
+      </c>
+      <c r="C12" s="7">
+        <v>260</v>
+      </c>
+      <c r="D12" s="11">
+        <v>290630</v>
+      </c>
+      <c r="E12" s="10">
+        <v>273900</v>
+      </c>
+      <c r="F12" s="11">
+        <v>27275</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12" s="12">
+        <f>AVERAGE(C11:C13)</f>
+        <v>266.666666666667</v>
+      </c>
+      <c r="I12" s="12">
+        <f>AVERAGE(D11:D13)</f>
+        <v>266640</v>
+      </c>
+      <c r="J12" s="12">
+        <f>AVERAGE(F11:F13)</f>
+        <v>27275</v>
+      </c>
+      <c r="K12" s="45">
         <f t="shared" si="5"/>
-        <v>127.434010703334</v>
-      </c>
-      <c r="Q11" s="15">
-        <f t="shared" si="6"/>
-        <v>69.3874916310922</v>
-      </c>
-    </row>
-    <row r="12" spans="2:17">
-      <c r="B12" s="12">
-        <v>8</v>
-      </c>
-      <c r="C12" s="12">
-        <v>260</v>
-      </c>
-      <c r="D12" s="13">
-        <v>290630</v>
-      </c>
-      <c r="E12" s="13">
-        <v>27275</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="G12" s="15">
-        <f t="shared" ref="G12:I12" si="17">AVERAGE(C11:C13)</f>
-        <v>266.666666666667</v>
-      </c>
-      <c r="H12" s="15">
+        <v>269686.666666667</v>
+      </c>
+      <c r="L12" s="12">
+        <f t="shared" ref="L12:N12" si="17">LN(H12)</f>
+        <v>5.58599943899982</v>
+      </c>
+      <c r="M12" s="12">
         <f t="shared" si="17"/>
-        <v>266640</v>
-      </c>
-      <c r="I12" s="15">
+        <v>12.4936547129816</v>
+      </c>
+      <c r="N12" s="46">
         <f t="shared" si="17"/>
-        <v>27275</v>
-      </c>
-      <c r="J12" s="15">
-        <f t="shared" ref="J12:L12" si="18">LN(G12)</f>
-        <v>5.58599943899982</v>
-      </c>
-      <c r="K12" s="15">
+        <v>10.2137258107013</v>
+      </c>
+      <c r="O12" s="47">
+        <f t="shared" si="7"/>
+        <v>12.505016070259</v>
+      </c>
+      <c r="P12" s="48">
+        <f t="shared" si="8"/>
+        <v>104.320194936185</v>
+      </c>
+      <c r="Q12" s="12">
+        <f t="shared" si="1"/>
+        <v>31.2033897325063</v>
+      </c>
+      <c r="R12" s="12">
+        <f t="shared" si="9"/>
+        <v>156.375426917435</v>
+      </c>
+      <c r="S12" s="12">
+        <f t="shared" si="2"/>
+        <v>57.0538666486753</v>
+      </c>
+      <c r="T12" s="12">
+        <f t="shared" si="3"/>
+        <v>127.60676361197</v>
+      </c>
+      <c r="U12" s="46">
+        <f t="shared" si="4"/>
+        <v>69.7895482177728</v>
+      </c>
+      <c r="V12" s="57">
+        <f t="shared" si="10"/>
+        <v>69.8530127531503</v>
+      </c>
+      <c r="W12" s="57">
+        <f t="shared" si="11"/>
+        <v>156.233352962102</v>
+      </c>
+      <c r="X12" s="57">
+        <f t="shared" si="12"/>
+        <v>127.722805400038</v>
+      </c>
+    </row>
+    <row r="13" spans="2:24">
+      <c r="B13" s="7">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7">
+        <v>280</v>
+      </c>
+      <c r="D13" s="11">
+        <v>233240</v>
+      </c>
+      <c r="E13" s="10">
+        <v>261260</v>
+      </c>
+      <c r="F13" s="10">
+        <v>27300</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H13" s="12">
+        <f>AVERAGE(C12:C14)</f>
+        <v>276.666666666667</v>
+      </c>
+      <c r="I13" s="12">
+        <f>AVERAGE(D12:D14)</f>
+        <v>253270</v>
+      </c>
+      <c r="J13" s="12">
+        <f>AVERAGE(F12:F14)</f>
+        <v>27291.6666666667</v>
+      </c>
+      <c r="K13" s="45">
+        <f t="shared" si="5"/>
+        <v>271388.333333333</v>
+      </c>
+      <c r="L13" s="12">
+        <f t="shared" ref="L13:N13" si="18">LN(H13)</f>
+        <v>5.62281341212253</v>
+      </c>
+      <c r="M13" s="12">
         <f t="shared" si="18"/>
-        <v>12.4936547129816</v>
-      </c>
-      <c r="L12" s="15">
+        <v>12.4422113923392</v>
+      </c>
+      <c r="N13" s="46">
         <f t="shared" si="18"/>
-        <v>10.2137258107013</v>
-      </c>
-      <c r="M12" s="15">
+        <v>10.2143366842694</v>
+      </c>
+      <c r="O13" s="47">
+        <f t="shared" si="7"/>
+        <v>12.5113060384779</v>
+      </c>
+      <c r="P13" s="48">
+        <f t="shared" si="8"/>
+        <v>104.332673899612</v>
+      </c>
+      <c r="Q13" s="12">
+        <f t="shared" si="1"/>
+        <v>31.6160306675451</v>
+      </c>
+      <c r="R13" s="12">
+        <f t="shared" si="9"/>
+        <v>156.532778788452</v>
+      </c>
+      <c r="S13" s="12">
         <f t="shared" si="2"/>
-        <v>104.320194936185</v>
-      </c>
-      <c r="N12" s="15">
+        <v>57.4333093042454</v>
+      </c>
+      <c r="T13" s="12">
         <f t="shared" si="3"/>
-        <v>31.2033897325063</v>
-      </c>
-      <c r="O12" s="15">
+        <v>127.088936258205</v>
+      </c>
+      <c r="U13" s="46">
         <f t="shared" si="4"/>
-        <v>57.0538666486753</v>
-      </c>
-      <c r="P12" s="15">
+        <v>69.9602330933086</v>
+      </c>
+      <c r="V13" s="57">
+        <f t="shared" si="10"/>
+        <v>70.3487393963229</v>
+      </c>
+      <c r="W13" s="57">
+        <f t="shared" si="11"/>
+        <v>155.668314524991</v>
+      </c>
+      <c r="X13" s="57">
+        <f t="shared" si="12"/>
+        <v>127.794692236946</v>
+      </c>
+    </row>
+    <row r="14" spans="2:24">
+      <c r="B14" s="7">
+        <v>10</v>
+      </c>
+      <c r="C14" s="7">
+        <v>290</v>
+      </c>
+      <c r="D14" s="11">
+        <v>235940</v>
+      </c>
+      <c r="E14" s="10">
+        <v>279005</v>
+      </c>
+      <c r="F14" s="10">
+        <v>27300</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="H14" s="12">
+        <f>AVERAGE(C13:C15)</f>
+        <v>286.666666666667</v>
+      </c>
+      <c r="I14" s="12">
+        <f>AVERAGE(D13:D15)</f>
+        <v>237566.666666667</v>
+      </c>
+      <c r="J14" s="12">
+        <f>AVERAGE(F13:F15)</f>
+        <v>27333.3333333333</v>
+      </c>
+      <c r="K14" s="45">
         <f t="shared" si="5"/>
-        <v>127.60676361197</v>
-      </c>
-      <c r="Q12" s="15">
-        <f t="shared" si="6"/>
-        <v>69.7895482177728</v>
-      </c>
-    </row>
-    <row r="13" spans="2:17">
-      <c r="B13" s="12">
-        <v>9</v>
-      </c>
-      <c r="C13" s="12">
-        <v>280</v>
-      </c>
-      <c r="D13" s="13">
-        <v>233240</v>
-      </c>
-      <c r="E13" s="13">
-        <v>27300</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="G13" s="15">
-        <f t="shared" ref="G13:I13" si="19">AVERAGE(C12:C14)</f>
+        <v>276425</v>
+      </c>
+      <c r="L14" s="12">
+        <f t="shared" ref="L14:N14" si="19">LN(H14)</f>
+        <v>5.65832010057944</v>
+      </c>
+      <c r="M14" s="12">
+        <f t="shared" si="19"/>
+        <v>12.3782035648219</v>
+      </c>
+      <c r="N14" s="46">
+        <f t="shared" si="19"/>
+        <v>10.2158622375783</v>
+      </c>
+      <c r="O14" s="47">
+        <f t="shared" si="7"/>
+        <v>12.5296948154106</v>
+      </c>
+      <c r="P14" s="48">
+        <f t="shared" si="8"/>
+        <v>104.363841257178</v>
+      </c>
+      <c r="Q14" s="12">
+        <f t="shared" si="1"/>
+        <v>32.0165863606214</v>
+      </c>
+      <c r="R14" s="12">
+        <f t="shared" si="9"/>
+        <v>156.993252167327</v>
+      </c>
+      <c r="S14" s="12">
+        <f t="shared" si="2"/>
+        <v>57.8046186436397</v>
+      </c>
+      <c r="T14" s="12">
+        <f t="shared" si="3"/>
+        <v>126.45402236692</v>
+      </c>
+      <c r="U14" s="46">
+        <f t="shared" si="4"/>
+        <v>70.0398380398956</v>
+      </c>
+      <c r="V14" s="57">
+        <f t="shared" si="10"/>
+        <v>70.8970240281639</v>
+      </c>
+      <c r="W14" s="57">
+        <f t="shared" si="11"/>
+        <v>155.095113030245</v>
+      </c>
+      <c r="X14" s="57">
+        <f t="shared" si="12"/>
+        <v>128.001636113134</v>
+      </c>
+    </row>
+    <row r="15" spans="2:24">
+      <c r="B15" s="7">
+        <v>11</v>
+      </c>
+      <c r="C15" s="7">
+        <v>290</v>
+      </c>
+      <c r="D15" s="11">
+        <v>243520</v>
+      </c>
+      <c r="E15" s="10">
+        <v>289010</v>
+      </c>
+      <c r="F15" s="10">
+        <v>27400</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H15" s="12">
+        <f>AVERAGE(C14:C16)</f>
+        <v>290</v>
+      </c>
+      <c r="I15" s="12">
+        <f>AVERAGE(D14:D16)</f>
+        <v>245483.333333333</v>
+      </c>
+      <c r="J15" s="12">
+        <f>AVERAGE(F14:F16)</f>
+        <v>27400</v>
+      </c>
+      <c r="K15" s="45">
+        <f t="shared" si="5"/>
+        <v>278051.666666667</v>
+      </c>
+      <c r="L15" s="12">
+        <f t="shared" ref="L15:N15" si="20">LN(H15)</f>
+        <v>5.66988092298052</v>
+      </c>
+      <c r="M15" s="12">
+        <f t="shared" si="20"/>
+        <v>12.4109843352496</v>
+      </c>
+      <c r="N15" s="46">
+        <f t="shared" si="20"/>
+        <v>10.2182982923762</v>
+      </c>
+      <c r="O15" s="47">
+        <f t="shared" si="7"/>
+        <v>12.5355622267235</v>
+      </c>
+      <c r="P15" s="48">
+        <f t="shared" si="8"/>
+        <v>104.413619991978</v>
+      </c>
+      <c r="Q15" s="12">
+        <f t="shared" si="1"/>
+        <v>32.1475496807784</v>
+      </c>
+      <c r="R15" s="12">
+        <f t="shared" si="9"/>
+        <v>157.140320340057</v>
+      </c>
+      <c r="S15" s="12">
+        <f t="shared" si="2"/>
+        <v>57.936534553268</v>
+      </c>
+      <c r="T15" s="12">
+        <f t="shared" si="3"/>
+        <v>126.819140039588</v>
+      </c>
+      <c r="U15" s="46">
+        <f t="shared" si="4"/>
+        <v>70.3688033178417</v>
+      </c>
+      <c r="V15" s="57">
+        <f t="shared" si="10"/>
+        <v>71.0751451281348</v>
+      </c>
+      <c r="W15" s="57">
+        <f t="shared" si="11"/>
+        <v>155.578666429412</v>
+      </c>
+      <c r="X15" s="57">
+        <f t="shared" si="12"/>
+        <v>128.092114095304</v>
+      </c>
+    </row>
+    <row r="16" spans="2:24">
+      <c r="B16" s="7">
+        <v>12</v>
+      </c>
+      <c r="C16" s="7">
+        <v>290</v>
+      </c>
+      <c r="D16" s="11">
+        <v>256990</v>
+      </c>
+      <c r="E16" s="10">
+        <v>266140</v>
+      </c>
+      <c r="F16" s="10">
+        <v>27500</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="H16" s="12">
+        <f>AVERAGE(C15:C17)</f>
         <v>276.666666666667</v>
       </c>
-      <c r="H13" s="15">
-        <f t="shared" si="19"/>
-        <v>253270</v>
-      </c>
-      <c r="I13" s="15">
-        <f t="shared" si="19"/>
-        <v>27291.6666666667</v>
-      </c>
-      <c r="J13" s="15">
-        <f t="shared" ref="J13:L13" si="20">LN(G13)</f>
+      <c r="I16" s="12">
+        <f>AVERAGE(D15:D17)</f>
+        <v>251530</v>
+      </c>
+      <c r="J16" s="12">
+        <f>AVERAGE(F15:F17)</f>
+        <v>27466.6666666667</v>
+      </c>
+      <c r="K16" s="45">
+        <f t="shared" si="5"/>
+        <v>262380</v>
+      </c>
+      <c r="L16" s="12">
+        <f t="shared" ref="L16:N16" si="21">LN(H16)</f>
         <v>5.62281341212253</v>
       </c>
-      <c r="K13" s="15">
-        <f t="shared" si="20"/>
-        <v>12.4422113923392</v>
-      </c>
-      <c r="L13" s="15">
-        <f t="shared" si="20"/>
-        <v>10.2143366842694</v>
-      </c>
-      <c r="M13" s="15">
+      <c r="M16" s="12">
+        <f t="shared" si="21"/>
+        <v>12.4353175457024</v>
+      </c>
+      <c r="N16" s="46">
+        <f t="shared" si="21"/>
+        <v>10.2207284272295</v>
+      </c>
+      <c r="O16" s="47">
+        <f t="shared" si="7"/>
+        <v>12.477549113635</v>
+      </c>
+      <c r="P16" s="48">
+        <f t="shared" si="8"/>
+        <v>104.463289583176</v>
+      </c>
+      <c r="Q16" s="12">
+        <f t="shared" si="1"/>
+        <v>31.6160306675451</v>
+      </c>
+      <c r="R16" s="12">
+        <f t="shared" si="9"/>
+        <v>155.689231883174</v>
+      </c>
+      <c r="S16" s="12">
         <f t="shared" si="2"/>
-        <v>104.332673899612</v>
-      </c>
-      <c r="N13" s="15">
+        <v>57.4692488822878</v>
+      </c>
+      <c r="T16" s="12">
         <f t="shared" si="3"/>
-        <v>31.6160306675451</v>
-      </c>
-      <c r="O13" s="15">
+        <v>127.098003540985</v>
+      </c>
+      <c r="U16" s="46">
         <f t="shared" si="4"/>
-        <v>57.4333093042454</v>
-      </c>
-      <c r="P13" s="15">
+        <v>69.9214702799779</v>
+      </c>
+      <c r="V16" s="57">
+        <f t="shared" si="10"/>
+        <v>70.1589305065646</v>
+      </c>
+      <c r="W16" s="57">
+        <f t="shared" si="11"/>
+        <v>155.162285420149</v>
+      </c>
+      <c r="X16" s="57">
+        <f t="shared" si="12"/>
+        <v>127.529640927881</v>
+      </c>
+    </row>
+    <row r="17" spans="2:24">
+      <c r="B17" s="7">
+        <v>13</v>
+      </c>
+      <c r="C17" s="7">
+        <v>250</v>
+      </c>
+      <c r="D17" s="11">
+        <v>254080</v>
+      </c>
+      <c r="E17" s="10">
+        <v>231990</v>
+      </c>
+      <c r="F17" s="10">
+        <v>27500</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H17" s="12">
+        <f>AVERAGE(C16:C18)</f>
+        <v>263.333333333333</v>
+      </c>
+      <c r="I17" s="12">
+        <f>AVERAGE(D16:D18)</f>
+        <v>257510</v>
+      </c>
+      <c r="J17" s="12">
+        <f>AVERAGE(F16:F18)</f>
+        <v>27666.6666666667</v>
+      </c>
+      <c r="K17" s="45">
         <f t="shared" si="5"/>
-        <v>127.088936258205</v>
-      </c>
-      <c r="Q13" s="15">
-        <f t="shared" si="6"/>
-        <v>69.9602330933086</v>
-      </c>
-    </row>
-    <row r="14" spans="2:17">
-      <c r="B14" s="12">
-        <v>10</v>
-      </c>
-      <c r="C14" s="12">
-        <v>290</v>
-      </c>
-      <c r="D14" s="13">
-        <v>235940</v>
-      </c>
-      <c r="E14" s="13">
-        <v>27300</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="G14" s="15">
-        <f t="shared" ref="G14:I14" si="21">AVERAGE(C13:C15)</f>
-        <v>286.666666666667</v>
-      </c>
-      <c r="H14" s="15">
-        <f t="shared" si="21"/>
-        <v>237566.666666667</v>
-      </c>
-      <c r="I14" s="15">
-        <f t="shared" si="21"/>
-        <v>27333.3333333333</v>
-      </c>
-      <c r="J14" s="15">
-        <f t="shared" ref="J14:L14" si="22">LN(G14)</f>
-        <v>5.65832010057944</v>
-      </c>
-      <c r="K14" s="15">
+        <v>249366.666666667</v>
+      </c>
+      <c r="L17" s="12">
+        <f t="shared" ref="L17:N17" si="22">LN(H17)</f>
+        <v>5.57342065679296</v>
+      </c>
+      <c r="M17" s="12">
         <f t="shared" si="22"/>
-        <v>12.3782035648219</v>
-      </c>
-      <c r="L14" s="15">
+        <v>12.4588138332833</v>
+      </c>
+      <c r="N17" s="46">
         <f t="shared" si="22"/>
-        <v>10.2158622375783</v>
-      </c>
-      <c r="M14" s="15">
+        <v>10.2279835981106</v>
+      </c>
+      <c r="O17" s="47">
+        <f t="shared" si="7"/>
+        <v>12.4266796491924</v>
+      </c>
+      <c r="P17" s="48">
+        <f t="shared" si="8"/>
+        <v>104.61164848322</v>
+      </c>
+      <c r="Q17" s="12">
+        <f t="shared" si="1"/>
+        <v>31.0630178175664</v>
+      </c>
+      <c r="R17" s="12">
+        <f t="shared" si="9"/>
+        <v>154.422367103652</v>
+      </c>
+      <c r="S17" s="12">
         <f t="shared" si="2"/>
-        <v>104.363841257178</v>
-      </c>
-      <c r="N14" s="15">
+        <v>57.0048550630493</v>
+      </c>
+      <c r="T17" s="12">
         <f t="shared" si="3"/>
-        <v>32.0165863606214</v>
-      </c>
-      <c r="O14" s="15">
+        <v>127.428543538736</v>
+      </c>
+      <c r="U17" s="46">
         <f t="shared" si="4"/>
-        <v>57.8046186436397</v>
-      </c>
-      <c r="P14" s="15">
+        <v>69.4382103775591</v>
+      </c>
+      <c r="V17" s="57">
+        <f t="shared" si="10"/>
+        <v>69.2591130521575</v>
+      </c>
+      <c r="W17" s="57">
+        <f t="shared" si="11"/>
+        <v>154.821688315139</v>
+      </c>
+      <c r="X17" s="57">
+        <f t="shared" si="12"/>
+        <v>127.099875630915</v>
+      </c>
+    </row>
+    <row r="18" spans="2:24">
+      <c r="B18" s="7">
+        <v>14</v>
+      </c>
+      <c r="C18" s="7">
+        <v>250</v>
+      </c>
+      <c r="D18" s="11">
+        <v>261460</v>
+      </c>
+      <c r="E18" s="10">
+        <v>249970</v>
+      </c>
+      <c r="F18" s="10">
+        <v>28000</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H18" s="12">
+        <f>AVERAGE(C17:C19)</f>
+        <v>250</v>
+      </c>
+      <c r="I18" s="12">
+        <f>AVERAGE(D17:D19)</f>
+        <v>259583.333333333</v>
+      </c>
+      <c r="J18" s="12">
+        <f>AVERAGE(F17:F19)</f>
+        <v>27833.3333333333</v>
+      </c>
+      <c r="K18" s="45">
         <f t="shared" si="5"/>
-        <v>126.45402236692</v>
-      </c>
-      <c r="Q14" s="15">
-        <f t="shared" si="6"/>
-        <v>70.0398380398956</v>
-      </c>
-    </row>
-    <row r="15" spans="2:17">
-      <c r="B15" s="12">
-        <v>11</v>
-      </c>
-      <c r="C15" s="12">
-        <v>290</v>
-      </c>
-      <c r="D15" s="13">
-        <v>243520</v>
-      </c>
-      <c r="E15" s="13">
-        <v>27400</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G15" s="15">
-        <f t="shared" ref="G15:I15" si="23">AVERAGE(C14:C16)</f>
-        <v>290</v>
-      </c>
-      <c r="H15" s="15">
+        <v>250803.333333333</v>
+      </c>
+      <c r="L18" s="12">
+        <f t="shared" ref="L18:N18" si="23">LN(H18)</f>
+        <v>5.52146091786225</v>
+      </c>
+      <c r="M18" s="12">
         <f t="shared" si="23"/>
-        <v>245483.333333333</v>
-      </c>
-      <c r="I15" s="15">
+        <v>12.4668330604157</v>
+      </c>
+      <c r="N18" s="46">
         <f t="shared" si="23"/>
-        <v>27400</v>
-      </c>
-      <c r="J15" s="15">
-        <f t="shared" ref="J15:L15" si="24">LN(G15)</f>
-        <v>5.66988092298052</v>
-      </c>
-      <c r="K15" s="15">
+        <v>10.2339896221708</v>
+      </c>
+      <c r="O18" s="47">
+        <f t="shared" si="7"/>
+        <v>12.4324243784553</v>
+      </c>
+      <c r="P18" s="48">
+        <f t="shared" si="8"/>
+        <v>104.7345435867</v>
+      </c>
+      <c r="Q18" s="12">
+        <f t="shared" si="1"/>
+        <v>30.4865306674802</v>
+      </c>
+      <c r="R18" s="12">
+        <f t="shared" si="9"/>
+        <v>154.565175926011</v>
+      </c>
+      <c r="S18" s="12">
+        <f t="shared" si="2"/>
+        <v>56.5065737326241</v>
+      </c>
+      <c r="T18" s="12">
+        <f t="shared" si="3"/>
+        <v>127.58544016163</v>
+      </c>
+      <c r="U18" s="46">
+        <f t="shared" si="4"/>
+        <v>68.8351315125982</v>
+      </c>
+      <c r="V18" s="57">
+        <f t="shared" si="10"/>
+        <v>68.645145319919</v>
+      </c>
+      <c r="W18" s="57">
+        <f t="shared" si="11"/>
+        <v>154.992959262445</v>
+      </c>
+      <c r="X18" s="57">
+        <f t="shared" si="12"/>
+        <v>127.233302067536</v>
+      </c>
+    </row>
+    <row r="19" spans="2:24">
+      <c r="B19" s="7">
+        <v>15</v>
+      </c>
+      <c r="C19" s="7">
+        <v>250</v>
+      </c>
+      <c r="D19" s="11">
+        <v>263210</v>
+      </c>
+      <c r="E19" s="10">
+        <v>270450</v>
+      </c>
+      <c r="F19" s="10">
+        <v>28000</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="H19" s="12">
+        <f>AVERAGE(C18:C20)</f>
+        <v>250</v>
+      </c>
+      <c r="I19" s="12">
+        <f>AVERAGE(D18:D20)</f>
+        <v>264456.666666667</v>
+      </c>
+      <c r="J19" s="12">
+        <f>AVERAGE(F18:F20)</f>
+        <v>28000</v>
+      </c>
+      <c r="K19" s="45">
+        <f t="shared" si="5"/>
+        <v>263623.333333333</v>
+      </c>
+      <c r="L19" s="12">
+        <f t="shared" ref="L19:N19" si="24">LN(H19)</f>
+        <v>5.52146091786225</v>
+      </c>
+      <c r="M19" s="12">
         <f t="shared" si="24"/>
-        <v>12.4109843352496</v>
-      </c>
-      <c r="L15" s="15">
+        <v>12.4854326857308</v>
+      </c>
+      <c r="N19" s="46">
         <f t="shared" si="24"/>
-        <v>10.2182982923762</v>
-      </c>
-      <c r="M15" s="15">
+        <v>10.2399597891573</v>
+      </c>
+      <c r="O19" s="47">
+        <f t="shared" si="7"/>
+        <v>12.4822765956495</v>
+      </c>
+      <c r="P19" s="48">
+        <f t="shared" si="8"/>
+        <v>104.856776483559</v>
+      </c>
+      <c r="Q19" s="12">
+        <f t="shared" si="1"/>
+        <v>30.4865306674802</v>
+      </c>
+      <c r="R19" s="12">
+        <f t="shared" si="9"/>
+        <v>155.807229010299</v>
+      </c>
+      <c r="S19" s="12">
         <f t="shared" si="2"/>
-        <v>104.413619991978</v>
-      </c>
-      <c r="N15" s="15">
+        <v>56.5395377763132</v>
+      </c>
+      <c r="T19" s="12">
         <f t="shared" si="3"/>
-        <v>32.1475496807784</v>
-      </c>
-      <c r="O15" s="15">
+        <v>127.850328652114</v>
+      </c>
+      <c r="U19" s="46">
         <f t="shared" si="4"/>
-        <v>57.936534553268</v>
-      </c>
-      <c r="P15" s="15">
+        <v>68.9378286168624</v>
+      </c>
+      <c r="V19" s="57">
+        <f t="shared" si="10"/>
+        <v>68.9204023888254</v>
+      </c>
+      <c r="W19" s="57">
+        <f t="shared" si="11"/>
+        <v>155.846624199655</v>
+      </c>
+      <c r="X19" s="57">
+        <f t="shared" si="12"/>
+        <v>127.818010416591</v>
+      </c>
+    </row>
+    <row r="20" spans="2:24">
+      <c r="B20" s="7">
+        <v>16</v>
+      </c>
+      <c r="C20" s="7">
+        <v>250</v>
+      </c>
+      <c r="D20" s="11">
+        <v>268700</v>
+      </c>
+      <c r="E20" s="10">
+        <v>270450</v>
+      </c>
+      <c r="F20" s="10">
+        <v>28000</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H20" s="12">
+        <f>AVERAGE(C19:C21)</f>
+        <v>250</v>
+      </c>
+      <c r="I20" s="12">
+        <f>AVERAGE(D19:D21)</f>
+        <v>270176.666666667</v>
+      </c>
+      <c r="J20" s="12">
+        <f>AVERAGE(F19:F21)</f>
+        <v>28000</v>
+      </c>
+      <c r="K20" s="45">
         <f t="shared" si="5"/>
-        <v>126.819140039588</v>
-      </c>
-      <c r="Q15" s="15">
-        <f t="shared" si="6"/>
-        <v>70.3688033178417</v>
-      </c>
-    </row>
-    <row r="16" spans="2:17">
-      <c r="B16" s="12">
-        <v>12</v>
-      </c>
-      <c r="C16" s="12">
-        <v>290</v>
-      </c>
-      <c r="D16" s="13">
-        <v>256990</v>
-      </c>
-      <c r="E16" s="13">
-        <v>27500</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="G16" s="15">
-        <f t="shared" ref="G16:I16" si="25">AVERAGE(C15:C17)</f>
-        <v>276.666666666667</v>
-      </c>
-      <c r="H16" s="15">
+        <v>270450</v>
+      </c>
+      <c r="L20" s="12">
+        <f t="shared" ref="L20:N20" si="25">LN(H20)</f>
+        <v>5.52146091786225</v>
+      </c>
+      <c r="M20" s="12">
         <f t="shared" si="25"/>
-        <v>251530</v>
-      </c>
-      <c r="I16" s="15">
+        <v>12.5068313449935</v>
+      </c>
+      <c r="N20" s="46">
         <f t="shared" si="25"/>
-        <v>27466.6666666667</v>
-      </c>
-      <c r="J16" s="15">
-        <f t="shared" ref="J16:L16" si="26">LN(G16)</f>
-        <v>5.62281341212253</v>
-      </c>
-      <c r="K16" s="15">
+        <v>10.2399597891573</v>
+      </c>
+      <c r="O20" s="47">
+        <f t="shared" si="7"/>
+        <v>12.5078425172996</v>
+      </c>
+      <c r="P20" s="48">
+        <f t="shared" si="8"/>
+        <v>104.856776483559</v>
+      </c>
+      <c r="Q20" s="12">
+        <f t="shared" si="1"/>
+        <v>30.4865306674802</v>
+      </c>
+      <c r="R20" s="12">
+        <f t="shared" si="9"/>
+        <v>156.446124437567</v>
+      </c>
+      <c r="S20" s="12">
+        <f t="shared" si="2"/>
+        <v>56.5395377763132</v>
+      </c>
+      <c r="T20" s="12">
+        <f t="shared" si="3"/>
+        <v>128.069450062506</v>
+      </c>
+      <c r="U20" s="46">
+        <f t="shared" si="4"/>
+        <v>69.0559804776762</v>
+      </c>
+      <c r="V20" s="57">
+        <f t="shared" si="10"/>
+        <v>69.0615636260453</v>
+      </c>
+      <c r="W20" s="57">
+        <f t="shared" si="11"/>
+        <v>156.433476853605</v>
+      </c>
+      <c r="X20" s="57">
+        <f t="shared" si="12"/>
+        <v>128.07980442626</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1" spans="2:24">
+      <c r="B21" s="7">
+        <v>17</v>
+      </c>
+      <c r="C21" s="7">
+        <v>250</v>
+      </c>
+      <c r="D21" s="11">
+        <v>278620</v>
+      </c>
+      <c r="E21" s="10">
+        <v>270450</v>
+      </c>
+      <c r="F21" s="10">
+        <v>28000</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="H21" s="12">
+        <f>AVERAGE(C20:C22)</f>
+        <v>256</v>
+      </c>
+      <c r="I21" s="12">
+        <f>AVERAGE(D20:D22)</f>
+        <v>276430</v>
+      </c>
+      <c r="J21" s="12">
+        <f>AVERAGE(F20:F22)</f>
+        <v>28000</v>
+      </c>
+      <c r="K21" s="45">
+        <f t="shared" si="5"/>
+        <v>267836.666666667</v>
+      </c>
+      <c r="L21" s="12">
+        <f t="shared" ref="L21:N21" si="26">LN(H21)</f>
+        <v>5.54517744447956</v>
+      </c>
+      <c r="M21" s="12">
         <f t="shared" si="26"/>
-        <v>12.4353175457024</v>
-      </c>
-      <c r="L16" s="15">
+        <v>12.529712903336</v>
+      </c>
+      <c r="N21" s="46">
         <f t="shared" si="26"/>
-        <v>10.2207284272295</v>
-      </c>
-      <c r="M16" s="15">
+        <v>10.2399597891573</v>
+      </c>
+      <c r="O21" s="47">
+        <f t="shared" si="7"/>
+        <v>12.4981326209649</v>
+      </c>
+      <c r="P21" s="48">
+        <f t="shared" si="8"/>
+        <v>104.856776483559</v>
+      </c>
+      <c r="Q21" s="12">
+        <f t="shared" si="1"/>
+        <v>30.7489928907649</v>
+      </c>
+      <c r="R21" s="12">
+        <f t="shared" si="9"/>
+        <v>156.203319011226</v>
+      </c>
+      <c r="S21" s="12">
         <f t="shared" si="2"/>
-        <v>104.463289583176</v>
-      </c>
-      <c r="N16" s="15">
+        <v>56.782394055213</v>
+      </c>
+      <c r="T21" s="12">
         <f t="shared" si="3"/>
-        <v>31.6160306675451</v>
-      </c>
-      <c r="O16" s="15">
+        <v>128.303756299847</v>
+      </c>
+      <c r="U21" s="46">
         <f t="shared" si="4"/>
-        <v>57.4692488822878</v>
-      </c>
-      <c r="P16" s="15">
+        <v>69.4794813773834</v>
+      </c>
+      <c r="V21" s="57">
+        <f t="shared" si="10"/>
+        <v>69.3043631078886</v>
+      </c>
+      <c r="W21" s="57">
+        <f t="shared" si="11"/>
+        <v>156.598013568508</v>
+      </c>
+      <c r="X21" s="57">
+        <f t="shared" si="12"/>
+        <v>127.980375478236</v>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1" spans="2:24">
+      <c r="B22" s="7">
+        <v>18</v>
+      </c>
+      <c r="C22" s="7">
+        <v>268</v>
+      </c>
+      <c r="D22" s="11">
+        <v>281970</v>
+      </c>
+      <c r="E22" s="10">
+        <v>262610</v>
+      </c>
+      <c r="F22" s="10">
+        <v>28000</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="H22" s="12">
+        <f>AVERAGE(C21:C23)</f>
+        <v>272.666666666667</v>
+      </c>
+      <c r="I22" s="12">
+        <f>AVERAGE(D21:D23)</f>
+        <v>282813.333333333</v>
+      </c>
+      <c r="J22" s="12">
+        <f>AVERAGE(F21:F23)</f>
+        <v>28333.3333333333</v>
+      </c>
+      <c r="K22" s="45">
         <f t="shared" si="5"/>
-        <v>127.098003540985</v>
-      </c>
-      <c r="Q16" s="15">
-        <f t="shared" si="6"/>
-        <v>69.9214702799779</v>
-      </c>
-    </row>
-    <row r="17" spans="2:17">
-      <c r="B17" s="12">
-        <v>13</v>
-      </c>
-      <c r="C17" s="12">
-        <v>250</v>
-      </c>
-      <c r="D17" s="13">
-        <v>254080</v>
-      </c>
-      <c r="E17" s="13">
-        <v>27500</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="G17" s="15">
-        <f t="shared" ref="G17:I17" si="27">AVERAGE(C16:C18)</f>
-        <v>263.333333333333</v>
-      </c>
-      <c r="H17" s="15">
+        <v>264391.666666667</v>
+      </c>
+      <c r="L22" s="12">
+        <f t="shared" ref="L22:N22" si="27">LN(H22)</f>
+        <v>5.60825004793464</v>
+      </c>
+      <c r="M22" s="12">
         <f t="shared" si="27"/>
-        <v>257510</v>
-      </c>
-      <c r="I17" s="15">
+        <v>12.552542359465</v>
+      </c>
+      <c r="N22" s="46">
         <f t="shared" si="27"/>
-        <v>27666.6666666667</v>
-      </c>
-      <c r="J17" s="15">
-        <f t="shared" ref="J17:L17" si="28">LN(G17)</f>
-        <v>5.57342065679296</v>
-      </c>
-      <c r="K17" s="15">
+        <v>10.2517942468043</v>
+      </c>
+      <c r="O22" s="47">
+        <f t="shared" si="7"/>
+        <v>12.4851868685608</v>
+      </c>
+      <c r="P22" s="48">
+        <f t="shared" si="8"/>
+        <v>105.099285278811</v>
+      </c>
+      <c r="Q22" s="12">
+        <f t="shared" si="1"/>
+        <v>31.4524686001589</v>
+      </c>
+      <c r="R22" s="12">
+        <f t="shared" si="9"/>
+        <v>155.879891142883</v>
+      </c>
+      <c r="S22" s="12">
+        <f t="shared" si="2"/>
+        <v>57.4946255760565</v>
+      </c>
+      <c r="T22" s="12">
+        <f t="shared" si="3"/>
+        <v>128.686081543532</v>
+      </c>
+      <c r="U22" s="46">
+        <f t="shared" si="4"/>
+        <v>70.3977962891714</v>
+      </c>
+      <c r="V22" s="57">
+        <f t="shared" si="10"/>
+        <v>70.020049854079</v>
+      </c>
+      <c r="W22" s="57">
+        <f t="shared" si="11"/>
+        <v>156.720837033446</v>
+      </c>
+      <c r="X22" s="57">
+        <f t="shared" si="12"/>
+        <v>127.995566909389</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" spans="2:24">
+      <c r="B23" s="7">
+        <v>19</v>
+      </c>
+      <c r="C23" s="7">
+        <v>300</v>
+      </c>
+      <c r="D23" s="11">
+        <v>287850</v>
+      </c>
+      <c r="E23" s="10">
+        <v>260115</v>
+      </c>
+      <c r="F23" s="10">
+        <v>29000</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H23" s="12">
+        <f>AVERAGE(C22:C24)</f>
+        <v>289.333333333333</v>
+      </c>
+      <c r="I23" s="12">
+        <f>AVERAGE(D22:D24)</f>
+        <v>285890</v>
+      </c>
+      <c r="J23" s="12">
+        <f>AVERAGE(F22:F24)</f>
+        <v>28666.6666666667</v>
+      </c>
+      <c r="K23" s="45">
+        <f t="shared" si="5"/>
+        <v>260946.666666667</v>
+      </c>
+      <c r="L23" s="12">
+        <f t="shared" ref="L23:N23" si="28">LN(H23)</f>
+        <v>5.66757942599224</v>
+      </c>
+      <c r="M23" s="12">
         <f t="shared" si="28"/>
-        <v>12.4588138332833</v>
-      </c>
-      <c r="L17" s="15">
+        <v>12.5633624004339</v>
+      </c>
+      <c r="N23" s="46">
         <f t="shared" si="28"/>
-        <v>10.2279835981106</v>
-      </c>
-      <c r="M17" s="15">
+        <v>10.2634902865675</v>
+      </c>
+      <c r="O23" s="47">
+        <f t="shared" si="7"/>
+        <v>12.4720713231508</v>
+      </c>
+      <c r="P23" s="48">
+        <f t="shared" si="8"/>
+        <v>105.339232862466</v>
+      </c>
+      <c r="Q23" s="12">
+        <f t="shared" si="1"/>
+        <v>32.1214565499305</v>
+      </c>
+      <c r="R23" s="12">
+        <f t="shared" si="9"/>
+        <v>155.55256308976</v>
+      </c>
+      <c r="S23" s="12">
         <f t="shared" si="2"/>
-        <v>104.61164848322</v>
-      </c>
-      <c r="N17" s="15">
+        <v>58.1691463870214</v>
+      </c>
+      <c r="T23" s="12">
         <f t="shared" si="3"/>
-        <v>31.0630178175664</v>
-      </c>
-      <c r="O17" s="15">
+        <v>128.943947963481</v>
+      </c>
+      <c r="U23" s="46">
         <f t="shared" si="4"/>
-        <v>57.0048550630493</v>
-      </c>
-      <c r="P17" s="15">
+        <v>71.2038542619837</v>
+      </c>
+      <c r="V23" s="57">
+        <f t="shared" si="10"/>
+        <v>70.6864548305973</v>
+      </c>
+      <c r="W23" s="57">
+        <f t="shared" si="11"/>
+        <v>156.691151916803</v>
+      </c>
+      <c r="X23" s="57">
+        <f t="shared" si="12"/>
+        <v>128.006982878536</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1" spans="2:24">
+      <c r="B24" s="13">
+        <v>20</v>
+      </c>
+      <c r="C24" s="13">
+        <v>300</v>
+      </c>
+      <c r="D24" s="14">
+        <v>287850</v>
+      </c>
+      <c r="E24" s="10">
+        <v>260115</v>
+      </c>
+      <c r="F24" s="10">
+        <v>29000</v>
+      </c>
+      <c r="G24" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="H24" s="16">
+        <f>AVERAGE(C23:C25)</f>
+        <v>303.333333333333</v>
+      </c>
+      <c r="I24" s="16">
+        <f>AVERAGE(D23:D25)</f>
+        <v>289736.666666667</v>
+      </c>
+      <c r="J24" s="16">
+        <f>AVERAGE(F23:F25)</f>
+        <v>29000</v>
+      </c>
+      <c r="K24" s="45">
         <f t="shared" si="5"/>
-        <v>127.428543538736</v>
-      </c>
-      <c r="Q17" s="15">
-        <f t="shared" si="6"/>
-        <v>69.4382103775591</v>
-      </c>
-    </row>
-    <row r="18" spans="2:17">
-      <c r="B18" s="12">
-        <v>14</v>
-      </c>
-      <c r="C18" s="12">
-        <v>250</v>
-      </c>
-      <c r="D18" s="13">
-        <v>261460</v>
-      </c>
-      <c r="E18" s="13">
-        <v>28000</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="G18" s="15">
-        <f t="shared" ref="G18:I18" si="29">AVERAGE(C17:C19)</f>
-        <v>250</v>
-      </c>
-      <c r="H18" s="15">
+        <v>262686.666666667</v>
+      </c>
+      <c r="L24" s="16">
+        <f t="shared" ref="L24:N24" si="29">LN(H24)</f>
+        <v>5.71483231084279</v>
+      </c>
+      <c r="M24" s="16">
         <f t="shared" si="29"/>
-        <v>259583.333333333</v>
-      </c>
-      <c r="I18" s="15">
+        <v>12.5767277434622</v>
+      </c>
+      <c r="N24" s="49">
         <f t="shared" si="29"/>
-        <v>27833.3333333333</v>
-      </c>
-      <c r="J18" s="15">
-        <f t="shared" ref="J18:L18" si="30">LN(G18)</f>
-        <v>5.52146091786225</v>
-      </c>
-      <c r="K18" s="15">
-        <f t="shared" si="30"/>
-        <v>12.4668330604157</v>
-      </c>
-      <c r="L18" s="15">
-        <f t="shared" si="30"/>
-        <v>10.2339896221708</v>
-      </c>
-      <c r="M18" s="15">
+        <v>10.2750511089686</v>
+      </c>
+      <c r="O24" s="47">
+        <f t="shared" si="7"/>
+        <v>12.4787172194052</v>
+      </c>
+      <c r="P24" s="50">
+        <f t="shared" si="8"/>
+        <v>105.576675291917</v>
+      </c>
+      <c r="Q24" s="16">
+        <f t="shared" si="1"/>
+        <v>32.6593083410527</v>
+      </c>
+      <c r="R24" s="12">
+        <f t="shared" si="9"/>
+        <v>155.71838344188</v>
+      </c>
+      <c r="S24" s="16">
         <f t="shared" si="2"/>
-        <v>104.7345435867</v>
-      </c>
-      <c r="N18" s="15">
+        <v>58.7201940730948</v>
+      </c>
+      <c r="T24" s="16">
         <f t="shared" si="3"/>
-        <v>30.4865306674802</v>
-      </c>
-      <c r="O18" s="15">
+        <v>129.226520347657</v>
+      </c>
+      <c r="U24" s="49">
         <f t="shared" si="4"/>
-        <v>56.5065737326241</v>
-      </c>
-      <c r="P18" s="15">
+        <v>71.8738900730104</v>
+      </c>
+      <c r="V24" s="57">
+        <f t="shared" si="10"/>
+        <v>71.3137763633272</v>
+      </c>
+      <c r="W24" s="57">
+        <f t="shared" si="11"/>
+        <v>156.941429056113</v>
+      </c>
+      <c r="X24" s="57">
+        <f t="shared" si="12"/>
+        <v>128.219457203755</v>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1" spans="2:24">
+      <c r="B25" s="13">
+        <v>21</v>
+      </c>
+      <c r="C25" s="13">
+        <v>310</v>
+      </c>
+      <c r="D25" s="14">
+        <v>293510</v>
+      </c>
+      <c r="E25" s="10">
+        <v>267830</v>
+      </c>
+      <c r="F25" s="10">
+        <v>29000</v>
+      </c>
+      <c r="G25" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="H25" s="16">
+        <f>AVERAGE(C24:C26)</f>
+        <v>353.333333333333</v>
+      </c>
+      <c r="I25" s="16">
+        <f>AVERAGE(D24:D26)</f>
+        <v>297495.333333333</v>
+      </c>
+      <c r="J25" s="16">
+        <f>AVERAGE(F24:F26)</f>
+        <v>30000</v>
+      </c>
+      <c r="K25" s="45">
         <f t="shared" si="5"/>
-        <v>127.58544016163</v>
-      </c>
-      <c r="Q18" s="15">
-        <f t="shared" si="6"/>
-        <v>68.8351315125982</v>
-      </c>
-    </row>
-    <row r="19" spans="2:17">
-      <c r="B19" s="12">
-        <v>15</v>
-      </c>
-      <c r="C19" s="12">
-        <v>250</v>
-      </c>
-      <c r="D19" s="13">
-        <v>263210</v>
-      </c>
-      <c r="E19" s="13">
-        <v>28000</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="G19" s="15">
-        <f t="shared" ref="G19:I19" si="31">AVERAGE(C18:C20)</f>
-        <v>250</v>
-      </c>
-      <c r="H19" s="15">
-        <f t="shared" si="31"/>
-        <v>264456.666666667</v>
-      </c>
-      <c r="I19" s="15">
-        <f t="shared" si="31"/>
-        <v>28000</v>
-      </c>
-      <c r="J19" s="15">
-        <f t="shared" ref="J19:L19" si="32">LN(G19)</f>
-        <v>5.52146091786225</v>
-      </c>
-      <c r="K19" s="15">
-        <f t="shared" si="32"/>
-        <v>12.4854326857308</v>
-      </c>
-      <c r="L19" s="15">
-        <f t="shared" si="32"/>
-        <v>10.2399597891573</v>
-      </c>
-      <c r="M19" s="15">
-        <f t="shared" si="2"/>
-        <v>104.856776483559</v>
-      </c>
-      <c r="N19" s="15">
-        <f t="shared" si="3"/>
-        <v>30.4865306674802</v>
-      </c>
-      <c r="O19" s="15">
-        <f t="shared" si="4"/>
-        <v>56.5395377763132</v>
-      </c>
-      <c r="P19" s="15">
+        <v>265108.333333333</v>
+      </c>
+      <c r="L25" s="16">
+        <f>LN(H25)</f>
+        <v>5.867411898438</v>
+      </c>
+      <c r="M25" s="16">
+        <f>LN(I25)</f>
+        <v>12.6031538175703</v>
+      </c>
+      <c r="N25" s="49">
+        <f>LN(J25)</f>
+        <v>10.3089526606443</v>
+      </c>
+      <c r="O25" s="47">
+        <f t="shared" si="7"/>
+        <v>12.4878938264618</v>
+      </c>
+      <c r="P25" s="50">
+        <f>N25*N25</f>
+        <v>106.274504959405</v>
+      </c>
+      <c r="Q25" s="16">
+        <f>L25*L25</f>
+        <v>34.4265223859319</v>
+      </c>
+      <c r="R25" s="12">
+        <f t="shared" si="9"/>
+        <v>155.947492220983</v>
+      </c>
+      <c r="S25" s="16">
+        <f>N25*L25</f>
+        <v>60.4868715014984</v>
+      </c>
+      <c r="T25" s="16">
+        <f>M25*N25</f>
+        <v>129.92531608015</v>
+      </c>
+      <c r="U25" s="49">
+        <f>M25*L25</f>
+        <v>73.9478946670562</v>
+      </c>
+      <c r="V25" s="57">
+        <f t="shared" si="10"/>
+        <v>73.2716168238124</v>
+      </c>
+      <c r="W25" s="57">
+        <f t="shared" si="11"/>
+        <v>157.386846752384</v>
+      </c>
+      <c r="X25" s="57">
+        <f t="shared" si="12"/>
+        <v>128.737106288147</v>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1" spans="2:24">
+      <c r="B26" s="13">
+        <v>22</v>
+      </c>
+      <c r="C26" s="13">
+        <v>450</v>
+      </c>
+      <c r="D26" s="14">
+        <v>311126</v>
+      </c>
+      <c r="E26" s="10">
+        <v>267380</v>
+      </c>
+      <c r="F26" s="10">
+        <v>32000</v>
+      </c>
+      <c r="G26" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="H26" s="16">
+        <f>AVERAGE(C25:C27)</f>
+        <v>403.333333333333</v>
+      </c>
+      <c r="I26" s="16">
+        <f>AVERAGE(D25:D27)</f>
+        <v>305585.333333333</v>
+      </c>
+      <c r="J26" s="16">
+        <f>AVERAGE(F25:F27)</f>
+        <v>31000</v>
+      </c>
+      <c r="K26" s="45">
         <f t="shared" si="5"/>
-        <v>127.850328652114</v>
-      </c>
-      <c r="Q19" s="15">
-        <f t="shared" si="6"/>
-        <v>68.9378286168624</v>
-      </c>
-    </row>
-    <row r="20" spans="2:17">
-      <c r="B20" s="12">
-        <v>16</v>
-      </c>
-      <c r="C20" s="12">
-        <v>250</v>
-      </c>
-      <c r="D20" s="13">
-        <v>268700</v>
-      </c>
-      <c r="E20" s="13">
-        <v>28000</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="G20" s="15">
-        <f t="shared" ref="G20:I20" si="33">AVERAGE(C19:C21)</f>
-        <v>250</v>
-      </c>
-      <c r="H20" s="15">
-        <f t="shared" si="33"/>
-        <v>270176.666666667</v>
-      </c>
-      <c r="I20" s="15">
-        <f t="shared" si="33"/>
-        <v>28000</v>
-      </c>
-      <c r="J20" s="15">
-        <f t="shared" ref="J20:L20" si="34">LN(G20)</f>
-        <v>5.52146091786225</v>
-      </c>
-      <c r="K20" s="15">
-        <f t="shared" si="34"/>
-        <v>12.5068313449935</v>
-      </c>
-      <c r="L20" s="15">
-        <f t="shared" si="34"/>
-        <v>10.2399597891573</v>
-      </c>
-      <c r="M20" s="15">
-        <f t="shared" si="2"/>
-        <v>104.856776483559</v>
-      </c>
-      <c r="N20" s="15">
-        <f t="shared" si="3"/>
-        <v>30.4865306674802</v>
-      </c>
-      <c r="O20" s="15">
-        <f t="shared" si="4"/>
-        <v>56.5395377763132</v>
-      </c>
-      <c r="P20" s="15">
+        <v>273945</v>
+      </c>
+      <c r="L26" s="16">
+        <f>LN(H26)</f>
+        <v>5.99976334992268</v>
+      </c>
+      <c r="M26" s="16">
+        <f>LN(I26)</f>
+        <v>12.6299843421036</v>
+      </c>
+      <c r="N26" s="49">
+        <f>LN(J26)</f>
+        <v>10.3417424834673</v>
+      </c>
+      <c r="O26" s="47">
+        <f t="shared" si="7"/>
+        <v>12.5206826352943</v>
+      </c>
+      <c r="P26" s="50">
+        <f>N26*N26</f>
+        <v>106.951637594352</v>
+      </c>
+      <c r="Q26" s="16">
+        <f>L26*L26</f>
+        <v>35.9971602550754</v>
+      </c>
+      <c r="R26" s="12">
+        <f t="shared" si="9"/>
+        <v>156.767493653759</v>
+      </c>
+      <c r="S26" s="16">
+        <f>N26*L26</f>
+        <v>62.0480075266453</v>
+      </c>
+      <c r="T26" s="16">
+        <f>M26*N26</f>
+        <v>130.616045636259</v>
+      </c>
+      <c r="U26" s="49">
+        <f>M26*L26</f>
+        <v>75.7769171658505</v>
+      </c>
+      <c r="V26" s="57">
+        <f t="shared" si="10"/>
+        <v>75.1211327912517</v>
+      </c>
+      <c r="W26" s="57">
+        <f t="shared" si="11"/>
+        <v>158.136025636215</v>
+      </c>
+      <c r="X26" s="57">
+        <f t="shared" si="12"/>
+        <v>129.485675531434</v>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1" spans="2:24">
+      <c r="B27" s="13">
+        <v>23</v>
+      </c>
+      <c r="C27" s="13">
+        <v>450</v>
+      </c>
+      <c r="D27" s="14">
+        <v>312120</v>
+      </c>
+      <c r="E27" s="10">
+        <v>286625</v>
+      </c>
+      <c r="F27" s="10">
+        <v>32000</v>
+      </c>
+      <c r="G27" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="H27" s="16">
+        <f>AVERAGE(C26:C28)</f>
+        <v>450</v>
+      </c>
+      <c r="I27" s="16">
+        <f>AVERAGE(D26:D28)</f>
+        <v>311623</v>
+      </c>
+      <c r="J27" s="16">
+        <f>AVERAGE(F26:F28)</f>
+        <v>32000</v>
+      </c>
+      <c r="K27" s="45">
         <f t="shared" si="5"/>
-        <v>128.069450062506</v>
-      </c>
-      <c r="Q20" s="15">
-        <f t="shared" si="6"/>
-        <v>69.0559804776762</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1" spans="2:17">
-      <c r="B21" s="12">
-        <v>17</v>
-      </c>
-      <c r="C21" s="12">
-        <v>250</v>
-      </c>
-      <c r="D21" s="13">
-        <v>278620</v>
-      </c>
-      <c r="E21" s="13">
-        <v>28000</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="G21" s="15">
-        <f t="shared" ref="G21:I21" si="35">AVERAGE(C20:C22)</f>
-        <v>256</v>
-      </c>
-      <c r="H21" s="15">
-        <f t="shared" si="35"/>
-        <v>276430</v>
-      </c>
-      <c r="I21" s="15">
-        <f t="shared" si="35"/>
-        <v>28000</v>
-      </c>
-      <c r="J21" s="15">
-        <f t="shared" ref="J21:L21" si="36">LN(G21)</f>
-        <v>5.54517744447956</v>
-      </c>
-      <c r="K21" s="15">
-        <f t="shared" si="36"/>
-        <v>12.529712903336</v>
-      </c>
-      <c r="L21" s="15">
-        <f t="shared" si="36"/>
-        <v>10.2399597891573</v>
-      </c>
-      <c r="M21" s="15">
-        <f t="shared" si="2"/>
-        <v>104.856776483559</v>
-      </c>
-      <c r="N21" s="15">
-        <f t="shared" si="3"/>
-        <v>30.7489928907649</v>
-      </c>
-      <c r="O21" s="15">
-        <f t="shared" si="4"/>
-        <v>56.782394055213</v>
-      </c>
-      <c r="P21" s="15">
-        <f t="shared" si="5"/>
-        <v>128.303756299847</v>
-      </c>
-      <c r="Q21" s="15">
-        <f t="shared" si="6"/>
-        <v>69.4794813773834</v>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1" spans="2:17">
-      <c r="B22" s="12">
-        <v>18</v>
-      </c>
-      <c r="C22" s="12">
-        <v>268</v>
-      </c>
-      <c r="D22" s="13">
-        <v>281970</v>
-      </c>
-      <c r="E22" s="13">
-        <v>28000</v>
-      </c>
-      <c r="F22" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="G22" s="15">
-        <f t="shared" ref="G22:I22" si="37">AVERAGE(C21:C23)</f>
-        <v>272.666666666667</v>
-      </c>
-      <c r="H22" s="15">
-        <f t="shared" si="37"/>
-        <v>282813.333333333</v>
-      </c>
-      <c r="I22" s="15">
-        <f t="shared" si="37"/>
-        <v>28333.3333333333</v>
-      </c>
-      <c r="J22" s="15">
-        <f t="shared" ref="J22:L22" si="38">LN(G22)</f>
-        <v>5.60825004793464</v>
-      </c>
-      <c r="K22" s="15">
-        <f t="shared" si="38"/>
-        <v>12.552542359465</v>
-      </c>
-      <c r="L22" s="15">
-        <f t="shared" si="38"/>
-        <v>10.2517942468043</v>
-      </c>
-      <c r="M22" s="15">
-        <f t="shared" si="2"/>
-        <v>105.099285278811</v>
-      </c>
-      <c r="N22" s="15">
-        <f t="shared" si="3"/>
-        <v>31.4524686001589</v>
-      </c>
-      <c r="O22" s="15">
-        <f t="shared" si="4"/>
-        <v>57.4946255760565</v>
-      </c>
-      <c r="P22" s="15">
-        <f t="shared" si="5"/>
-        <v>128.686081543532</v>
-      </c>
-      <c r="Q22" s="15">
-        <f t="shared" si="6"/>
-        <v>70.3977962891714</v>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1" spans="2:17">
-      <c r="B23" s="12">
-        <v>19</v>
-      </c>
-      <c r="C23" s="12">
-        <v>300</v>
-      </c>
-      <c r="D23" s="13">
-        <v>287850</v>
-      </c>
-      <c r="E23" s="13">
-        <v>29000</v>
-      </c>
-      <c r="F23" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="G23" s="15">
-        <f t="shared" ref="G23:I23" si="39">AVERAGE(C22:C24)</f>
-        <v>289.333333333333</v>
-      </c>
-      <c r="H23" s="15">
-        <f t="shared" si="39"/>
-        <v>285890</v>
-      </c>
-      <c r="I23" s="15">
-        <f t="shared" si="39"/>
-        <v>28666.6666666667</v>
-      </c>
-      <c r="J23" s="15">
-        <f t="shared" ref="J23:L23" si="40">LN(G23)</f>
-        <v>5.66757942599224</v>
-      </c>
-      <c r="K23" s="15">
-        <f t="shared" si="40"/>
-        <v>12.5633624004339</v>
-      </c>
-      <c r="L23" s="15">
-        <f t="shared" si="40"/>
-        <v>10.2634902865675</v>
-      </c>
-      <c r="M23" s="15">
-        <f t="shared" si="2"/>
-        <v>105.339232862466</v>
-      </c>
-      <c r="N23" s="15">
-        <f t="shared" si="3"/>
-        <v>32.1214565499305</v>
-      </c>
-      <c r="O23" s="15">
-        <f t="shared" si="4"/>
-        <v>58.1691463870214</v>
-      </c>
-      <c r="P23" s="15">
-        <f t="shared" si="5"/>
-        <v>128.943947963481</v>
-      </c>
-      <c r="Q23" s="15">
-        <f t="shared" si="6"/>
-        <v>71.2038542619837</v>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1" spans="2:17">
-      <c r="B24" s="16">
-        <v>20</v>
-      </c>
-      <c r="C24" s="16">
-        <v>300</v>
-      </c>
-      <c r="D24" s="17">
-        <v>287850</v>
-      </c>
-      <c r="E24" s="17">
-        <v>29000</v>
-      </c>
-      <c r="F24" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="G24" s="19">
-        <f t="shared" ref="G24:I24" si="41">AVERAGE(C23:C25)</f>
-        <v>300</v>
-      </c>
-      <c r="H24" s="19">
-        <f t="shared" si="41"/>
-        <v>287850</v>
-      </c>
-      <c r="I24" s="19">
-        <f t="shared" si="41"/>
-        <v>29000</v>
-      </c>
-      <c r="J24" s="19">
-        <f t="shared" ref="J24:L24" si="42">LN(G24)</f>
-        <v>5.7037824746562</v>
-      </c>
-      <c r="K24" s="19">
-        <f t="shared" si="42"/>
-        <v>12.570194790104</v>
-      </c>
-      <c r="L24" s="19">
-        <f t="shared" si="42"/>
-        <v>10.2750511089686</v>
-      </c>
-      <c r="M24" s="19">
-        <f t="shared" si="2"/>
-        <v>105.576675291917</v>
-      </c>
-      <c r="N24" s="19">
-        <f t="shared" si="3"/>
-        <v>32.5331345181952</v>
-      </c>
-      <c r="O24" s="19">
-        <f t="shared" si="4"/>
-        <v>58.6066564415319</v>
-      </c>
-      <c r="P24" s="19">
-        <f t="shared" si="5"/>
-        <v>129.159393918009</v>
-      </c>
-      <c r="Q24" s="19">
-        <f t="shared" si="6"/>
-        <v>71.6976567468096</v>
-      </c>
-    </row>
-    <row r="25" ht="15.75" customHeight="1" spans="2:17">
-      <c r="B25" s="20"/>
-      <c r="C25" s="20"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="21"/>
-      <c r="H25" s="21"/>
-      <c r="I25" s="21"/>
-      <c r="J25" s="21"/>
-      <c r="K25" s="21"/>
-      <c r="L25" s="21"/>
-      <c r="M25" s="21"/>
-      <c r="N25" s="21"/>
-      <c r="O25" s="21"/>
-      <c r="P25" s="21"/>
-      <c r="Q25" s="21"/>
-    </row>
-    <row r="26" ht="15.75" customHeight="1" spans="2:17">
-      <c r="B26" s="22"/>
-      <c r="C26" s="23"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="23"/>
-      <c r="H26" s="23"/>
-      <c r="I26" s="59"/>
-      <c r="J26" s="21"/>
-      <c r="K26" s="21"/>
-      <c r="L26" s="21"/>
-      <c r="M26" s="21"/>
-      <c r="N26" s="21"/>
-      <c r="O26" s="21"/>
-      <c r="P26" s="21"/>
-      <c r="Q26" s="21"/>
-    </row>
-    <row r="27" ht="15.75" customHeight="1" spans="2:17">
-      <c r="B27" s="20"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="21"/>
-      <c r="I27" s="21"/>
-      <c r="J27" s="21"/>
-      <c r="K27" s="21"/>
-      <c r="L27" s="21"/>
-      <c r="M27" s="21"/>
-      <c r="N27" s="21"/>
-      <c r="O27" s="21"/>
-      <c r="P27" s="21"/>
-      <c r="Q27" s="21"/>
-    </row>
-    <row r="28" ht="15.75" customHeight="1" spans="2:17">
-      <c r="B28" s="24">
-        <f>SUM(J6:J28)</f>
-        <v>106.215104862367</v>
-      </c>
-      <c r="C28" s="24">
-        <f t="shared" ref="C28:I28" si="43">SUM(K6:K27)</f>
-        <v>234.164412154255</v>
-      </c>
-      <c r="D28" s="24">
-        <f t="shared" si="43"/>
-        <v>194.15242961536</v>
-      </c>
-      <c r="E28" s="24">
-        <f t="shared" si="43"/>
-        <v>1983.97399005249</v>
-      </c>
-      <c r="F28" s="24">
-        <f t="shared" si="43"/>
-        <v>593.82767404388</v>
-      </c>
-      <c r="G28" s="24">
-        <f t="shared" si="43"/>
-        <v>1085.37639517285</v>
-      </c>
-      <c r="H28" s="24">
-        <f t="shared" si="43"/>
-        <v>2392.97997878471</v>
-      </c>
-      <c r="I28" s="60">
-        <f t="shared" si="43"/>
-        <v>1309.14967029363</v>
-      </c>
-      <c r="J28" s="61"/>
-      <c r="K28" s="62"/>
-      <c r="L28" s="62"/>
-      <c r="M28" s="62"/>
-      <c r="N28" s="62"/>
-      <c r="O28" s="62"/>
-      <c r="P28" s="62"/>
-      <c r="Q28" s="68"/>
-    </row>
-    <row r="29" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A29" s="25"/>
-      <c r="B29" s="26"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="27"/>
-      <c r="I29" s="63"/>
-    </row>
-    <row r="30" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A30" s="28"/>
-      <c r="I30" s="25"/>
-    </row>
-    <row r="31" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A31" s="29"/>
-      <c r="B31" s="30">
+        <v>277002.5</v>
+      </c>
+      <c r="L27" s="16">
+        <f>LN(H27)</f>
+        <v>6.10924758276437</v>
+      </c>
+      <c r="M27" s="16">
+        <f>LN(I27)</f>
+        <v>12.6495494028349</v>
+      </c>
+      <c r="N27" s="49">
+        <f>LN(J27)</f>
+        <v>10.3734911817819</v>
+      </c>
+      <c r="O27" s="47">
+        <f t="shared" si="7"/>
+        <v>12.5317818103995</v>
+      </c>
+      <c r="P27" s="50">
+        <f>N27*N27</f>
+        <v>107.609319298506</v>
+      </c>
+      <c r="Q27" s="16">
+        <f>L27*L27</f>
+        <v>37.3229060275122</v>
+      </c>
+      <c r="R27" s="12">
+        <f t="shared" si="9"/>
+        <v>157.04555534346</v>
+      </c>
+      <c r="S27" s="16">
+        <f>N27*L27</f>
+        <v>63.3742259271283</v>
+      </c>
+      <c r="T27" s="16">
+        <f>M27*N27</f>
+        <v>131.219989183822</v>
+      </c>
+      <c r="U27" s="49">
+        <f>M27*L27</f>
+        <v>77.2792291123278</v>
+      </c>
+      <c r="V27" s="57">
+        <f t="shared" si="10"/>
+        <v>76.5597577329136</v>
+      </c>
+      <c r="W27" s="57">
+        <f t="shared" si="11"/>
+        <v>158.521393116197</v>
+      </c>
+      <c r="X27" s="57">
+        <f t="shared" si="12"/>
+        <v>129.998328102194</v>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1" spans="2:21">
+      <c r="B28" s="17"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="18"/>
+      <c r="J28" s="18"/>
+      <c r="K28" s="20"/>
+      <c r="L28" s="20"/>
+      <c r="M28" s="20"/>
+      <c r="N28" s="20"/>
+      <c r="O28" s="20"/>
+      <c r="P28" s="20"/>
+      <c r="Q28" s="20"/>
+      <c r="R28" s="20"/>
+      <c r="S28" s="20"/>
+      <c r="T28" s="20"/>
+      <c r="U28" s="20"/>
+    </row>
+    <row r="29" ht="15.75" customHeight="1" spans="2:21">
+      <c r="B29" s="17"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="18"/>
+      <c r="I29" s="18"/>
+      <c r="J29" s="18"/>
+      <c r="K29" s="20"/>
+      <c r="L29" s="20"/>
+      <c r="M29" s="20"/>
+      <c r="N29" s="20"/>
+      <c r="O29" s="20"/>
+      <c r="P29" s="20"/>
+      <c r="Q29" s="20"/>
+      <c r="R29" s="20"/>
+      <c r="S29" s="20"/>
+      <c r="T29" s="20"/>
+      <c r="U29" s="20"/>
+    </row>
+    <row r="30" ht="15.75" customHeight="1" spans="2:21">
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="20"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="20"/>
+      <c r="K30" s="20"/>
+      <c r="L30" s="20"/>
+      <c r="M30" s="20"/>
+      <c r="N30" s="20"/>
+      <c r="O30" s="20"/>
+      <c r="P30" s="20"/>
+      <c r="Q30" s="20"/>
+      <c r="R30" s="20"/>
+      <c r="S30" s="20"/>
+      <c r="T30" s="20"/>
+      <c r="U30" s="20"/>
+    </row>
+    <row r="31" ht="15.75" customHeight="1" spans="2:21">
+      <c r="B31" s="21">
+        <f>SUM(L6:L27)</f>
+        <v>124.202577529679</v>
+      </c>
+      <c r="C31" s="21">
+        <f>SUM(M6:M27)</f>
+        <v>272.053632670122</v>
+      </c>
+      <c r="D31" s="21">
+        <f>SUM(N6:N27)</f>
+        <v>225.176615941253</v>
+      </c>
+      <c r="E31" s="21">
+        <f>SUM(O6:O27)</f>
+        <v>273.912112663857</v>
+      </c>
+      <c r="F31" s="21">
+        <f>SUM(P6:P27)</f>
+        <v>2304.80945190475</v>
+      </c>
+      <c r="G31" s="21">
+        <f>SUM(Q6:Q27)</f>
+        <v>701.700436535257</v>
+      </c>
+      <c r="H31" s="21">
+        <f>SUM(S6:S27)</f>
+        <v>1271.39903775968</v>
+      </c>
+      <c r="I31" s="21">
+        <f>SUM(T6:T27)</f>
+        <v>2784.80845611459</v>
+      </c>
+      <c r="J31" s="51">
+        <f>SUM(U6:U27)</f>
+        <v>1536.32994456507</v>
+      </c>
+      <c r="K31" s="52">
+        <f>SUM(V6:V27)</f>
+        <v>1546.5182067027</v>
+      </c>
+      <c r="L31" s="52">
+        <f>SUM(W6:W27)</f>
+        <v>3387.90899169029</v>
+      </c>
+      <c r="M31" s="52">
+        <f>SUM(X6:X27)</f>
+        <v>2803.64429086975</v>
+      </c>
+      <c r="N31" s="18"/>
+      <c r="O31" s="18"/>
+      <c r="P31" s="18"/>
+      <c r="Q31" s="18"/>
+      <c r="R31" s="18"/>
+      <c r="S31" s="18"/>
+      <c r="T31" s="18"/>
+      <c r="U31" s="18"/>
+    </row>
+    <row r="32" ht="15.75" customHeight="1" spans="1:10">
+      <c r="A32" s="22"/>
+      <c r="B32" s="23"/>
+      <c r="C32" s="24"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="24"/>
+      <c r="H32" s="24"/>
+      <c r="I32" s="24"/>
+      <c r="J32" s="53"/>
+    </row>
+    <row r="33" ht="15.75" customHeight="1" spans="1:10">
+      <c r="A33" s="18"/>
+      <c r="J33" s="22"/>
+    </row>
+    <row r="34" ht="15.75" customHeight="1" spans="1:10">
+      <c r="A34" s="25"/>
+      <c r="B34" s="26">
         <v>1257</v>
       </c>
-      <c r="C31" s="30">
-        <f>$F$76*(D31^$F$77)*(B31^F78)</f>
-        <v>867920.941186815</v>
-      </c>
-      <c r="D31" s="30">
+      <c r="C34" s="26">
+        <f>$G$79*(D34^$G$80)*(B34^G81)</f>
+        <v>13412327.6155072</v>
+      </c>
+      <c r="D34" s="26">
         <v>60000</v>
       </c>
-      <c r="F31" s="30">
-        <f>AVERAGE(B31:B33)</f>
+      <c r="G34" s="26">
+        <f>AVERAGE(B34:B36)</f>
         <v>1258</v>
       </c>
-      <c r="G31" s="30">
-        <f>AVERAGE(C31:C33)</f>
-        <v>333358.813746239</v>
-      </c>
-      <c r="H31" s="30">
-        <f>AVERAGE(D31:D33)</f>
+      <c r="H34" s="26">
+        <f>AVERAGE(C34:C36)</f>
+        <v>890813569191.078</v>
+      </c>
+      <c r="I34" s="26">
+        <f>AVERAGE(D34:D36)</f>
         <v>60000</v>
       </c>
-      <c r="I31" s="28"/>
-    </row>
-    <row r="32" ht="15.75" customHeight="1" spans="1:4">
-      <c r="A32" s="25"/>
-      <c r="B32" s="30">
+      <c r="J34" s="18"/>
+    </row>
+    <row r="35" ht="15.75" customHeight="1" spans="1:4">
+      <c r="A35" s="22"/>
+      <c r="B35" s="26">
         <v>1258</v>
       </c>
-      <c r="C32" s="30">
-        <f>$F$76*(D32^$F$77)*(B32^F85)</f>
-        <v>66077.75002595</v>
-      </c>
-      <c r="D32" s="30">
+      <c r="C35" s="26">
+        <f>$G$79*(D35^$G$80)*(B35^G88)</f>
+        <v>1336213647622.81</v>
+      </c>
+      <c r="D35" s="26">
         <v>60000</v>
       </c>
     </row>
-    <row r="33" ht="15.75" customHeight="1" spans="1:4">
-      <c r="A33" s="28"/>
-      <c r="B33" s="30">
+    <row r="36" ht="15.75" customHeight="1" spans="1:4">
+      <c r="A36" s="18"/>
+      <c r="B36" s="27">
         <v>1259</v>
       </c>
-      <c r="C33" s="30">
-        <f>$F$76*(D33^$F$77)*(B33^F86)</f>
-        <v>66077.75002595</v>
-      </c>
-      <c r="D33" s="30">
+      <c r="C36" s="27">
+        <f>$G$79*(D36^$G$80)*(B36^G89)</f>
+        <v>1336213647622.81</v>
+      </c>
+      <c r="D36" s="27">
         <v>60000</v>
       </c>
     </row>
-    <row r="34" ht="15.75" customHeight="1" spans="2:10">
-      <c r="B34" s="31"/>
-      <c r="C34" s="27"/>
-      <c r="D34" s="27"/>
-      <c r="E34" s="27"/>
-      <c r="F34" s="27"/>
-      <c r="G34" s="27"/>
-      <c r="H34" s="27"/>
-      <c r="I34" s="27"/>
-      <c r="J34" s="34"/>
-    </row>
-    <row r="35" ht="15.75" customHeight="1"/>
-    <row r="36" ht="15.75" customHeight="1"/>
-    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="37" ht="15.75" customHeight="1" spans="2:12">
+      <c r="B37" s="28"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="29"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="29"/>
+      <c r="H37" s="29"/>
+      <c r="I37" s="29"/>
+      <c r="J37" s="29"/>
+      <c r="K37" s="54"/>
+      <c r="L37" s="55"/>
+    </row>
     <row r="38" ht="15.75" customHeight="1"/>
     <row r="39" ht="15.75" customHeight="1"/>
     <row r="40" ht="15.75" customHeight="1"/>
@@ -4596,1248 +5540,1319 @@
     <row r="53" ht="15.75" customHeight="1"/>
     <row r="54" ht="15.75" customHeight="1"/>
     <row r="55" ht="15.75" customHeight="1"/>
-    <row r="56" ht="15.75" customHeight="1" spans="1:7">
-      <c r="A56" s="32"/>
-      <c r="B56" s="33" t="s">
-        <v>41</v>
-      </c>
-      <c r="C56" s="34"/>
-      <c r="D56" s="35" t="s">
-        <v>42</v>
-      </c>
-      <c r="E56" s="36">
+    <row r="56" ht="15.75" customHeight="1"/>
+    <row r="57" ht="15.75" customHeight="1"/>
+    <row r="58" ht="15.75" customHeight="1"/>
+    <row r="59" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A59" s="30"/>
+      <c r="B59" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="C59" s="32"/>
+      <c r="D59" s="33"/>
+      <c r="E59" s="34"/>
+      <c r="F59" s="35"/>
+      <c r="G59" s="18"/>
+      <c r="H59" s="30"/>
+    </row>
+    <row r="60" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A60" s="30"/>
+      <c r="B60" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="C60" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="E60" s="38"/>
+      <c r="F60" s="38"/>
+      <c r="H60" s="30"/>
+    </row>
+    <row r="61" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A61" s="30"/>
+      <c r="B61" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="C61" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="H61" s="30"/>
+    </row>
+    <row r="62" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A62" s="30"/>
+      <c r="B62" s="36" t="s">
+        <v>56</v>
+      </c>
+      <c r="C62" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="H62" s="30"/>
+    </row>
+    <row r="63" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A63" s="30"/>
+      <c r="H63" s="30"/>
+    </row>
+    <row r="64" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A64" s="30"/>
+      <c r="B64" s="39" t="s">
+        <v>58</v>
+      </c>
+      <c r="C64" s="39" t="s">
+        <v>59</v>
+      </c>
+      <c r="D64" s="39" t="s">
+        <v>60</v>
+      </c>
+      <c r="G64" s="39" t="s">
+        <v>61</v>
+      </c>
+      <c r="H64" s="30"/>
+    </row>
+    <row r="65" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A65" s="30"/>
+      <c r="B65" s="58">
         <v>22</v>
       </c>
-      <c r="F56" s="37" t="s">
-        <v>43</v>
-      </c>
-      <c r="G56" s="38"/>
-    </row>
-    <row r="57" ht="15.75" customHeight="1" spans="1:7">
-      <c r="A57" s="39"/>
-      <c r="B57" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="C57" s="41" t="s">
-        <v>45</v>
-      </c>
-      <c r="E57" s="42"/>
-      <c r="G57" s="39"/>
-    </row>
-    <row r="58" ht="15.75" customHeight="1" spans="1:7">
-      <c r="A58" s="39"/>
-      <c r="B58" s="40" t="s">
-        <v>46</v>
-      </c>
-      <c r="C58" s="41" t="s">
-        <v>47</v>
-      </c>
-      <c r="G58" s="39"/>
-    </row>
-    <row r="59" ht="15.75" customHeight="1" spans="1:7">
-      <c r="A59" s="39"/>
-      <c r="B59" s="40" t="s">
-        <v>48</v>
-      </c>
-      <c r="C59" s="41" t="s">
-        <v>49</v>
-      </c>
-      <c r="G59" s="39"/>
-    </row>
-    <row r="60" ht="15.75" customHeight="1" spans="1:7">
-      <c r="A60" s="39"/>
-      <c r="G60" s="39"/>
-    </row>
-    <row r="61" ht="15.75" customHeight="1" spans="1:7">
-      <c r="A61" s="39"/>
-      <c r="B61" s="43" t="s">
-        <v>50</v>
-      </c>
-      <c r="C61" s="43" t="s">
-        <v>51</v>
-      </c>
-      <c r="D61" s="43" t="s">
+      <c r="C65" s="59">
+        <f>D31</f>
+        <v>225.176615941253</v>
+      </c>
+      <c r="D65" s="60">
+        <f>B31</f>
+        <v>124.202577529679</v>
+      </c>
+      <c r="E65" s="61"/>
+      <c r="F65" s="62" t="s">
+        <v>62</v>
+      </c>
+      <c r="G65" s="60">
+        <f>C31</f>
+        <v>272.053632670122</v>
+      </c>
+      <c r="H65" s="30"/>
+    </row>
+    <row r="66" ht="15.75" customHeight="1" spans="1:20">
+      <c r="A66" s="22"/>
+      <c r="B66" s="63"/>
+      <c r="C66" s="63"/>
+      <c r="D66" s="63"/>
+      <c r="E66" s="64"/>
+      <c r="F66" s="64"/>
+      <c r="G66" s="63"/>
+      <c r="H66" s="30"/>
+      <c r="I66" s="97"/>
+      <c r="J66" s="97"/>
+      <c r="K66" s="97"/>
+      <c r="L66" s="97"/>
+      <c r="M66" s="30"/>
+      <c r="N66" s="97"/>
+      <c r="O66" s="97"/>
+      <c r="P66" s="97"/>
+      <c r="Q66" s="107"/>
+      <c r="R66" s="108"/>
+      <c r="S66" s="109"/>
+      <c r="T66" s="107"/>
+    </row>
+    <row r="67" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A67" s="18"/>
+      <c r="B67" s="65" t="s">
+        <v>59</v>
+      </c>
+      <c r="C67" s="65" t="s">
+        <v>63</v>
+      </c>
+      <c r="D67" s="65" t="s">
+        <v>64</v>
+      </c>
+      <c r="E67" s="66"/>
+      <c r="F67" s="66"/>
+      <c r="G67" s="65" t="s">
+        <v>65</v>
+      </c>
+      <c r="H67" s="67"/>
+    </row>
+    <row r="68" ht="15.75" customHeight="1" spans="2:8">
+      <c r="B68" s="68">
+        <f>D31</f>
+        <v>225.176615941253</v>
+      </c>
+      <c r="C68" s="59">
+        <f>F31</f>
+        <v>2304.80945190475</v>
+      </c>
+      <c r="D68" s="60">
+        <f>H31</f>
+        <v>1271.39903775968</v>
+      </c>
+      <c r="E68" s="61"/>
+      <c r="F68" s="62" t="s">
+        <v>62</v>
+      </c>
+      <c r="G68" s="60">
+        <f>I31</f>
+        <v>2784.80845611459</v>
+      </c>
+      <c r="H68" s="67"/>
+    </row>
+    <row r="69" ht="15.75" customHeight="1" spans="2:8">
+      <c r="B69" s="66"/>
+      <c r="C69" s="66"/>
+      <c r="D69" s="66"/>
+      <c r="E69" s="66"/>
+      <c r="F69" s="66"/>
+      <c r="G69" s="66"/>
+      <c r="H69" s="67"/>
+    </row>
+    <row r="70" ht="15.75" customHeight="1" spans="2:8">
+      <c r="B70" s="65" t="s">
+        <v>60</v>
+      </c>
+      <c r="C70" s="65" t="s">
+        <v>64</v>
+      </c>
+      <c r="D70" s="65" t="s">
+        <v>66</v>
+      </c>
+      <c r="E70" s="66"/>
+      <c r="F70" s="66"/>
+      <c r="G70" s="65" t="s">
+        <v>67</v>
+      </c>
+      <c r="H70" s="67"/>
+    </row>
+    <row r="71" ht="15.75" customHeight="1" spans="2:8">
+      <c r="B71" s="68">
+        <f>B31</f>
+        <v>124.202577529679</v>
+      </c>
+      <c r="C71" s="59">
+        <f>H31</f>
+        <v>1271.39903775968</v>
+      </c>
+      <c r="D71" s="60">
+        <f>G31</f>
+        <v>701.700436535257</v>
+      </c>
+      <c r="E71" s="61"/>
+      <c r="F71" s="62" t="s">
+        <v>62</v>
+      </c>
+      <c r="G71" s="60">
+        <f>J31</f>
+        <v>1536.32994456507</v>
+      </c>
+      <c r="H71" s="67"/>
+    </row>
+    <row r="72" ht="15.75" customHeight="1" spans="8:8">
+      <c r="H72" s="67"/>
+    </row>
+    <row r="73" ht="15.75" customHeight="1" spans="8:8">
+      <c r="H73" s="67"/>
+    </row>
+    <row r="74" ht="15.75" customHeight="1" spans="8:8">
+      <c r="H74" s="67"/>
+    </row>
+    <row r="75" ht="15.75" customHeight="1" spans="2:8">
+      <c r="B75" s="65">
+        <f>B65</f>
+        <v>22</v>
+      </c>
+      <c r="C75" s="60">
+        <f>D31</f>
+        <v>225.176615941253</v>
+      </c>
+      <c r="D75" s="60">
+        <f>B31</f>
+        <v>124.202577529679</v>
+      </c>
+      <c r="E75" s="61"/>
+      <c r="F75" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="G75" s="60">
+        <f>C31</f>
+        <v>272.053632670122</v>
+      </c>
+      <c r="H75" s="67"/>
+    </row>
+    <row r="76" ht="15.75" customHeight="1" spans="2:8">
+      <c r="B76" s="65">
+        <f>D31</f>
+        <v>225.176615941253</v>
+      </c>
+      <c r="C76" s="60">
+        <f>F31</f>
+        <v>2304.80945190475</v>
+      </c>
+      <c r="D76" s="60">
+        <f>H31</f>
+        <v>1271.39903775968</v>
+      </c>
+      <c r="E76" s="61"/>
+      <c r="F76" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="G76" s="60">
+        <f>I31</f>
+        <v>2784.80845611459</v>
+      </c>
+      <c r="H76" s="67"/>
+    </row>
+    <row r="77" ht="15.75" customHeight="1" spans="2:8">
+      <c r="B77" s="65">
+        <f>B31</f>
+        <v>124.202577529679</v>
+      </c>
+      <c r="C77" s="60">
+        <f>H31</f>
+        <v>1271.39903775968</v>
+      </c>
+      <c r="D77" s="60">
+        <f>G31</f>
+        <v>701.700436535257</v>
+      </c>
+      <c r="E77" s="61"/>
+      <c r="F77" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="G77" s="60">
+        <f>J31</f>
+        <v>1536.32994456507</v>
+      </c>
+      <c r="H77" s="67"/>
+    </row>
+    <row r="78" ht="15.75" customHeight="1" spans="8:8">
+      <c r="H78" s="67"/>
+    </row>
+    <row r="79" ht="15.75" customHeight="1" spans="2:8">
+      <c r="B79" s="69" t="s">
         <v>52</v>
       </c>
-      <c r="F61" s="43" t="s">
-        <v>53</v>
-      </c>
-      <c r="G61" s="39"/>
-    </row>
-    <row r="62" ht="15.75" customHeight="1" spans="1:7">
-      <c r="A62" s="44"/>
-      <c r="B62" s="45">
-        <f>E56</f>
-        <v>22</v>
-      </c>
-      <c r="C62" s="46">
-        <f>D28</f>
-        <v>194.15242961536</v>
-      </c>
-      <c r="D62" s="47">
-        <f>B28</f>
-        <v>106.215104862367</v>
-      </c>
-      <c r="E62" s="48" t="s">
+      <c r="C79" s="70">
+        <f t="array" ref="C79:C81">MMULT(MINVERSE(B75:D77),G75:G77)</f>
+        <v>-64.6248554449121</v>
+      </c>
+      <c r="D79" s="71" t="s">
+        <v>69</v>
+      </c>
+      <c r="E79" s="72"/>
+      <c r="F79" s="73" t="s">
+        <v>70</v>
+      </c>
+      <c r="G79" s="70">
+        <f>EXP(C79)</f>
+        <v>8.58582211806365e-29</v>
+      </c>
+      <c r="H79" s="67"/>
+    </row>
+    <row r="80" ht="15.75" customHeight="1" spans="2:8">
+      <c r="B80" s="69" t="s">
         <v>54</v>
       </c>
-      <c r="F62" s="47">
-        <f>C28</f>
-        <v>234.164412154255</v>
-      </c>
-      <c r="G62" s="44"/>
-    </row>
-    <row r="63" ht="15.75" customHeight="1" spans="1:16">
-      <c r="A63" s="25"/>
-      <c r="B63" s="49"/>
-      <c r="C63" s="49"/>
-      <c r="D63" s="49"/>
-      <c r="E63" s="50"/>
-      <c r="F63" s="49"/>
-      <c r="G63" s="51"/>
-      <c r="H63" s="52"/>
-      <c r="I63" s="52"/>
-      <c r="J63" s="64"/>
-      <c r="K63" s="65"/>
-      <c r="L63" s="52"/>
-      <c r="M63" s="52"/>
-      <c r="N63" s="66"/>
-      <c r="O63" s="67"/>
-      <c r="P63" s="66"/>
-    </row>
-    <row r="64" ht="15.75" customHeight="1" spans="1:7">
-      <c r="A64" s="28"/>
-      <c r="B64" s="53" t="s">
-        <v>51</v>
-      </c>
-      <c r="C64" s="53" t="s">
-        <v>55</v>
-      </c>
-      <c r="D64" s="53" t="s">
+      <c r="C80" s="70">
+        <v>8.4116412207477</v>
+      </c>
+      <c r="D80" s="71" t="s">
+        <v>69</v>
+      </c>
+      <c r="E80" s="72"/>
+      <c r="F80" s="73" t="s">
+        <v>71</v>
+      </c>
+      <c r="G80" s="70">
+        <f t="shared" ref="G80:G81" si="30">C80</f>
+        <v>8.4116412207477</v>
+      </c>
+      <c r="H80" s="67"/>
+    </row>
+    <row r="81" ht="15.75" customHeight="1" spans="2:8">
+      <c r="B81" s="69" t="s">
         <v>56</v>
       </c>
-      <c r="E64" s="54"/>
-      <c r="F64" s="53" t="s">
-        <v>57</v>
-      </c>
-      <c r="G64" s="55"/>
-    </row>
-    <row r="65" ht="15.75" customHeight="1" spans="2:7">
-      <c r="B65" s="45">
-        <f t="shared" ref="B65:C65" si="44">D28</f>
-        <v>194.15242961536</v>
-      </c>
-      <c r="C65" s="46">
-        <f t="shared" si="44"/>
-        <v>1983.97399005249</v>
-      </c>
-      <c r="D65" s="47">
-        <f>G28</f>
-        <v>1085.37639517285</v>
-      </c>
-      <c r="E65" s="48" t="s">
-        <v>54</v>
-      </c>
-      <c r="F65" s="47">
-        <f>H28</f>
-        <v>2392.97997878471</v>
-      </c>
-      <c r="G65" s="55"/>
-    </row>
-    <row r="66" ht="15.75" customHeight="1" spans="2:7">
-      <c r="B66" s="54"/>
-      <c r="C66" s="54"/>
-      <c r="D66" s="54"/>
-      <c r="E66" s="54"/>
-      <c r="F66" s="54"/>
-      <c r="G66" s="55"/>
-    </row>
-    <row r="67" ht="15.75" customHeight="1" spans="2:7">
-      <c r="B67" s="53" t="s">
-        <v>52</v>
-      </c>
-      <c r="C67" s="53" t="s">
-        <v>56</v>
-      </c>
-      <c r="D67" s="53" t="s">
-        <v>58</v>
-      </c>
-      <c r="E67" s="54"/>
-      <c r="F67" s="53" t="s">
-        <v>59</v>
-      </c>
-      <c r="G67" s="55"/>
-    </row>
-    <row r="68" ht="15.75" customHeight="1" spans="2:7">
-      <c r="B68" s="45">
-        <f>B28</f>
-        <v>106.215104862367</v>
-      </c>
-      <c r="C68" s="46">
-        <f>G28</f>
-        <v>1085.37639517285</v>
-      </c>
-      <c r="D68" s="47">
-        <f>F28</f>
-        <v>593.82767404388</v>
-      </c>
-      <c r="E68" s="48" t="s">
-        <v>54</v>
-      </c>
-      <c r="F68" s="47">
-        <f>I28</f>
-        <v>1309.14967029363</v>
-      </c>
-      <c r="G68" s="55"/>
-    </row>
-    <row r="69" ht="15.75" customHeight="1" spans="7:7">
-      <c r="G69" s="55"/>
-    </row>
-    <row r="70" ht="15.75" customHeight="1" spans="7:7">
-      <c r="G70" s="55"/>
-    </row>
-    <row r="71" ht="15.75" customHeight="1" spans="7:7">
-      <c r="G71" s="55"/>
-    </row>
-    <row r="72" ht="15.75" customHeight="1" spans="2:7">
-      <c r="B72" s="69">
-        <f>E56</f>
-        <v>22</v>
-      </c>
-      <c r="C72" s="47">
-        <f>D28</f>
-        <v>194.15242961536</v>
-      </c>
-      <c r="D72" s="47">
-        <f>B28</f>
-        <v>106.215104862367</v>
-      </c>
-      <c r="E72" s="48" t="s">
-        <v>60</v>
-      </c>
-      <c r="F72" s="47">
-        <f>C28</f>
-        <v>234.164412154255</v>
-      </c>
-      <c r="G72" s="55"/>
-    </row>
-    <row r="73" ht="15.75" customHeight="1" spans="2:7">
-      <c r="B73" s="69">
-        <f t="shared" ref="B73:C73" si="45">D28</f>
-        <v>194.15242961536</v>
-      </c>
-      <c r="C73" s="47">
-        <f t="shared" si="45"/>
-        <v>1983.97399005249</v>
-      </c>
-      <c r="D73" s="47">
-        <f>G28</f>
-        <v>1085.37639517285</v>
-      </c>
-      <c r="E73" s="48" t="s">
-        <v>60</v>
-      </c>
-      <c r="F73" s="47">
-        <f>H28</f>
-        <v>2392.97997878471</v>
-      </c>
-      <c r="G73" s="55"/>
-    </row>
-    <row r="74" ht="15.75" customHeight="1" spans="2:7">
-      <c r="B74" s="69">
-        <f>B28</f>
-        <v>106.215104862367</v>
-      </c>
-      <c r="C74" s="47">
-        <f>G28</f>
-        <v>1085.37639517285</v>
-      </c>
-      <c r="D74" s="47">
-        <f>F28</f>
-        <v>593.82767404388</v>
-      </c>
-      <c r="E74" s="48" t="s">
-        <v>60</v>
-      </c>
-      <c r="F74" s="47">
-        <f>I28</f>
-        <v>1309.14967029363</v>
-      </c>
-      <c r="G74" s="55"/>
-    </row>
-    <row r="75" ht="15.75" customHeight="1" spans="7:7">
-      <c r="G75" s="55"/>
-    </row>
-    <row r="76" ht="15.75" customHeight="1" spans="2:7">
-      <c r="B76" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="C76" s="70">
-        <f t="array" ref="C76:C78">MMULT(MINVERSE(B72:D74),F72:F74)</f>
-        <v>-0.00447027369261832</v>
-      </c>
-      <c r="D76" s="71" t="s">
-        <v>61</v>
-      </c>
-      <c r="E76" s="72" t="s">
-        <v>62</v>
-      </c>
-      <c r="F76" s="70">
-        <f>EXP(C76)</f>
-        <v>0.995539703108944</v>
-      </c>
-      <c r="G76" s="55"/>
-    </row>
-    <row r="77" ht="15.75" customHeight="1" spans="2:7">
-      <c r="B77" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="C77" s="70">
-        <v>1.0091762292941</v>
-      </c>
-      <c r="D77" s="71" t="s">
-        <v>61</v>
-      </c>
-      <c r="E77" s="72" t="s">
-        <v>63</v>
-      </c>
-      <c r="F77" s="70">
-        <f t="shared" ref="F77:F78" si="46">C77</f>
-        <v>1.0091762292941</v>
-      </c>
-      <c r="G77" s="55"/>
-    </row>
-    <row r="78" ht="15.75" customHeight="1" spans="2:7">
-      <c r="B78" s="35" t="s">
-        <v>48</v>
-      </c>
-      <c r="C78" s="70">
-        <v>0.360859610296757</v>
-      </c>
-      <c r="D78" s="71" t="s">
-        <v>61</v>
-      </c>
-      <c r="E78" s="72" t="s">
-        <v>64</v>
-      </c>
-      <c r="F78" s="70">
-        <f>C78</f>
-        <v>0.360859610296757</v>
-      </c>
-      <c r="G78" s="55"/>
-    </row>
-    <row r="79" ht="15.75" customHeight="1" spans="7:7">
-      <c r="G79" s="55"/>
-    </row>
-    <row r="80" ht="15.75" customHeight="1" spans="2:7">
-      <c r="B80" s="2"/>
-      <c r="C80" s="71"/>
-      <c r="D80" s="2"/>
-      <c r="G80" s="55"/>
-    </row>
-    <row r="81" ht="15.75" customHeight="1" spans="2:7">
-      <c r="B81" s="73" t="s">
-        <v>65</v>
-      </c>
-      <c r="C81" s="74" t="s">
-        <v>66</v>
-      </c>
-      <c r="D81" s="74" t="s">
-        <v>67</v>
-      </c>
-      <c r="E81" s="74" t="s">
-        <v>68</v>
-      </c>
-      <c r="G81" s="55"/>
-    </row>
-    <row r="82" ht="15.75" customHeight="1" spans="2:7">
-      <c r="B82" s="53">
-        <f>H6</f>
+      <c r="C81" s="70">
+        <v>-1.61272379468028</v>
+      </c>
+      <c r="D81" s="71" t="s">
+        <v>69</v>
+      </c>
+      <c r="E81" s="72"/>
+      <c r="F81" s="73" t="s">
+        <v>72</v>
+      </c>
+      <c r="G81" s="70">
+        <f t="shared" si="30"/>
+        <v>-1.61272379468028</v>
+      </c>
+      <c r="H81" s="67"/>
+    </row>
+    <row r="82" ht="15.75" customHeight="1" spans="8:8">
+      <c r="H82" s="67"/>
+    </row>
+    <row r="83" ht="15.75" customHeight="1" spans="2:8">
+      <c r="B83" s="74"/>
+      <c r="C83" s="71"/>
+      <c r="D83" s="74"/>
+      <c r="H83" s="67"/>
+    </row>
+    <row r="84" ht="15.75" customHeight="1" spans="2:8">
+      <c r="B84" s="75" t="s">
+        <v>73</v>
+      </c>
+      <c r="C84" s="76" t="s">
+        <v>74</v>
+      </c>
+      <c r="D84" s="76" t="s">
+        <v>75</v>
+      </c>
+      <c r="E84" s="76"/>
+      <c r="F84" s="76" t="s">
+        <v>76</v>
+      </c>
+      <c r="H84" s="67"/>
+    </row>
+    <row r="85" ht="15.75" customHeight="1" spans="2:8">
+      <c r="B85" s="65">
+        <f>I6</f>
         <v>104200</v>
       </c>
-      <c r="C82" s="75">
-        <f t="shared" ref="C82:C100" si="47">$F$76*(I6^$F$77)*(G6^$F$78)</f>
-        <v>210465.590109774</v>
-      </c>
-      <c r="D82" s="75">
-        <f t="shared" ref="D82:D100" si="48">(B82-C82)^2</f>
-        <v>11292375641.3785</v>
-      </c>
-      <c r="E82" s="75">
-        <f t="shared" ref="E82:E100" si="49">(B82-$B$106)^2</f>
-        <v>16954050164.8507</v>
-      </c>
-      <c r="G82" s="55"/>
-    </row>
-    <row r="83" ht="15.75" customHeight="1" spans="2:7">
-      <c r="B83" s="53">
-        <f t="shared" ref="B82:B100" si="50">H7</f>
+      <c r="C85" s="77">
+        <f t="shared" ref="C85:C103" si="31">$G$79*(J6^$G$80)*(H6^$G$81)</f>
+        <v>144882.367822529</v>
+      </c>
+      <c r="D85" s="77">
+        <f t="shared" ref="D85:D103" si="32">(B85-C85)^2</f>
+        <v>1655055051.64752</v>
+      </c>
+      <c r="E85" s="77"/>
+      <c r="F85" s="77">
+        <f t="shared" ref="F85:F103" si="33">(B85-$B$109)^2</f>
+        <v>16979918821.1757</v>
+      </c>
+      <c r="H85" s="67"/>
+    </row>
+    <row r="86" ht="15.75" customHeight="1" spans="2:8">
+      <c r="B86" s="65">
+        <f t="shared" ref="B85:B103" si="34">I7</f>
         <v>110323.333333333</v>
       </c>
-      <c r="C83" s="75">
-        <f t="shared" si="47"/>
-        <v>208047.021651921</v>
-      </c>
-      <c r="D83" s="75">
-        <f t="shared" si="48"/>
-        <v>9549919258.58842</v>
-      </c>
-      <c r="E83" s="76">
-        <f>(B83-$B$106)^2</f>
-        <v>15396934840.2893</v>
-      </c>
-      <c r="G83" s="55"/>
-    </row>
-    <row r="84" ht="15.75" customHeight="1" spans="2:7">
-      <c r="B84" s="53">
-        <f t="shared" si="50"/>
+      <c r="C86" s="77">
+        <f t="shared" si="31"/>
+        <v>157717.436144641</v>
+      </c>
+      <c r="D86" s="77">
+        <f t="shared" si="32"/>
+        <v>2246200981.28883</v>
+      </c>
+      <c r="E86" s="78"/>
+      <c r="F86" s="78">
+        <f t="shared" si="33"/>
+        <v>15421587424.0997</v>
+      </c>
+      <c r="H86" s="67"/>
+    </row>
+    <row r="87" ht="15.75" customHeight="1" spans="2:8">
+      <c r="B87" s="65">
+        <f t="shared" si="34"/>
         <v>138140</v>
       </c>
-      <c r="C84" s="75">
-        <f t="shared" si="47"/>
-        <v>212251.401150609</v>
-      </c>
-      <c r="D84" s="75">
-        <f t="shared" si="48"/>
-        <v>5492499780.50647</v>
-      </c>
-      <c r="E84" s="75">
-        <f t="shared" si="49"/>
-        <v>9267473778.88581</v>
-      </c>
-      <c r="G84" s="55"/>
-    </row>
-    <row r="85" ht="15.75" customHeight="1" spans="2:7">
-      <c r="B85" s="53">
-        <f t="shared" si="50"/>
+      <c r="C87" s="77">
+        <f t="shared" si="31"/>
+        <v>157308.803449653</v>
+      </c>
+      <c r="D87" s="77">
+        <f t="shared" si="32"/>
+        <v>367443025.69142</v>
+      </c>
+      <c r="E87" s="77"/>
+      <c r="F87" s="77">
+        <f t="shared" si="33"/>
+        <v>9286602070.29855</v>
+      </c>
+      <c r="H87" s="67"/>
+    </row>
+    <row r="88" ht="15.75" customHeight="1" spans="2:8">
+      <c r="B88" s="65">
+        <f t="shared" si="34"/>
         <v>173040</v>
       </c>
-      <c r="C85" s="75">
-        <f t="shared" si="47"/>
-        <v>217513.375587255</v>
-      </c>
-      <c r="D85" s="75">
-        <f t="shared" si="48"/>
-        <v>1977881136.12503</v>
-      </c>
-      <c r="E85" s="75">
-        <f t="shared" si="49"/>
-        <v>3765996971.86826</v>
-      </c>
-      <c r="G85" s="55"/>
-    </row>
-    <row r="86" ht="15.75" customHeight="1" spans="2:7">
-      <c r="B86" s="53">
-        <f t="shared" si="50"/>
+      <c r="C88" s="77">
+        <f t="shared" si="31"/>
+        <v>171580.187543167</v>
+      </c>
+      <c r="D88" s="77">
+        <f t="shared" si="32"/>
+        <v>2131052.40912563</v>
+      </c>
+      <c r="E88" s="77"/>
+      <c r="F88" s="77">
+        <f t="shared" si="33"/>
+        <v>3778194245.73715</v>
+      </c>
+      <c r="H88" s="67"/>
+    </row>
+    <row r="89" ht="15.75" customHeight="1" spans="2:8">
+      <c r="B89" s="65">
+        <f t="shared" si="34"/>
         <v>226283.333333333</v>
       </c>
-      <c r="C86" s="75">
-        <f t="shared" si="47"/>
-        <v>222943.291916279</v>
-      </c>
-      <c r="D86" s="75">
-        <f t="shared" si="48"/>
-        <v>11155876.6676362</v>
-      </c>
-      <c r="E86" s="75">
-        <f t="shared" si="49"/>
-        <v>66005647.3068631</v>
-      </c>
-      <c r="F86" s="77"/>
-      <c r="G86" s="55"/>
-    </row>
-    <row r="87" ht="15.75" customHeight="1" spans="2:7">
-      <c r="B87" s="53">
-        <f t="shared" si="50"/>
+      <c r="C89" s="77">
+        <f t="shared" si="31"/>
+        <v>187953.710035047</v>
+      </c>
+      <c r="D89" s="77">
+        <f t="shared" si="32"/>
+        <v>1469160022.18851</v>
+      </c>
+      <c r="E89" s="77"/>
+      <c r="F89" s="77">
+        <f t="shared" si="33"/>
+        <v>67628981.9944594</v>
+      </c>
+      <c r="G89" s="79"/>
+      <c r="H89" s="67"/>
+    </row>
+    <row r="90" ht="15.75" customHeight="1" spans="2:8">
+      <c r="B90" s="65">
+        <f t="shared" si="34"/>
         <v>262560</v>
       </c>
-      <c r="C87" s="75">
-        <f t="shared" si="47"/>
-        <v>221542.637490226</v>
-      </c>
-      <c r="D87" s="75">
-        <f t="shared" si="48"/>
-        <v>1682424027.25818</v>
-      </c>
-      <c r="E87" s="75">
-        <f t="shared" si="49"/>
-        <v>792550908.710374</v>
-      </c>
-      <c r="F87" s="77"/>
-      <c r="G87" s="55"/>
-    </row>
-    <row r="88" ht="15.75" customHeight="1" spans="2:6">
-      <c r="B88" s="53">
-        <f t="shared" si="50"/>
+      <c r="C90" s="77">
+        <f t="shared" si="31"/>
+        <v>222173.013144553</v>
+      </c>
+      <c r="D90" s="77">
+        <f t="shared" si="32"/>
+        <v>1631108707.26208</v>
+      </c>
+      <c r="E90" s="77"/>
+      <c r="F90" s="77">
+        <f t="shared" si="33"/>
+        <v>786969824.684519</v>
+      </c>
+      <c r="G90" s="79"/>
+      <c r="H90" s="67"/>
+    </row>
+    <row r="91" ht="15.75" customHeight="1" spans="2:7">
+      <c r="B91" s="65">
+        <f t="shared" si="34"/>
         <v>266640</v>
       </c>
-      <c r="C88" s="75">
-        <f t="shared" si="47"/>
-        <v>223852.046893974</v>
-      </c>
-      <c r="D88" s="75">
-        <f t="shared" si="48"/>
-        <v>1830808931.00346</v>
-      </c>
-      <c r="E88" s="75">
-        <f t="shared" si="49"/>
-        <v>1038919919.23669</v>
-      </c>
-      <c r="F88" s="77"/>
-    </row>
-    <row r="89" ht="15.75" customHeight="1" spans="1:6">
-      <c r="A89" s="78"/>
-      <c r="B89" s="53">
-        <f t="shared" si="50"/>
+      <c r="C91" s="77">
+        <f t="shared" si="31"/>
+        <v>215489.484056091</v>
+      </c>
+      <c r="D91" s="77">
+        <f t="shared" si="32"/>
+        <v>2616375281.32811</v>
+      </c>
+      <c r="E91" s="77"/>
+      <c r="F91" s="77">
+        <f t="shared" si="33"/>
+        <v>1032528561.52662</v>
+      </c>
+      <c r="G91" s="79"/>
+    </row>
+    <row r="92" ht="15.75" customHeight="1" spans="1:7">
+      <c r="A92" s="80"/>
+      <c r="B92" s="65">
+        <f t="shared" si="34"/>
         <v>253270</v>
       </c>
-      <c r="C89" s="75">
-        <f t="shared" si="47"/>
-        <v>226985.578304872</v>
-      </c>
-      <c r="D89" s="75">
-        <f t="shared" si="48"/>
-        <v>690870823.847309</v>
-      </c>
-      <c r="E89" s="75">
-        <f t="shared" si="49"/>
-        <v>355785633.271777</v>
-      </c>
-      <c r="F89" s="77"/>
-    </row>
-    <row r="90" ht="15.75" customHeight="1" spans="1:16">
-      <c r="A90" s="79"/>
-      <c r="B90" s="53">
-        <f t="shared" si="50"/>
+      <c r="C92" s="77">
+        <f t="shared" si="31"/>
+        <v>204114.230247794</v>
+      </c>
+      <c r="D92" s="77">
+        <f t="shared" si="32"/>
+        <v>2416289699.93192</v>
+      </c>
+      <c r="E92" s="77"/>
+      <c r="F92" s="77">
+        <f t="shared" si="33"/>
+        <v>352049510.649431</v>
+      </c>
+      <c r="G92" s="79"/>
+    </row>
+    <row r="93" ht="15.75" customHeight="1" spans="1:20">
+      <c r="A93" s="81"/>
+      <c r="B93" s="65">
+        <f t="shared" si="34"/>
         <v>237566.666666667</v>
       </c>
-      <c r="C90" s="75">
-        <f t="shared" si="47"/>
-        <v>230266.875762125</v>
-      </c>
-      <c r="D90" s="75">
-        <f t="shared" si="48"/>
-        <v>53286947.2500319</v>
-      </c>
-      <c r="E90" s="75">
-        <f t="shared" si="49"/>
-        <v>9978948.47645439</v>
-      </c>
-      <c r="F90" s="77"/>
-      <c r="M90" s="104"/>
-      <c r="N90" s="67"/>
-      <c r="O90" s="67"/>
-      <c r="P90" s="66"/>
-    </row>
-    <row r="91" ht="15.75" customHeight="1" spans="2:6">
-      <c r="B91" s="53">
-        <f t="shared" si="50"/>
+      <c r="C93" s="77">
+        <f t="shared" si="31"/>
+        <v>195243.932965479</v>
+      </c>
+      <c r="D93" s="77">
+        <f t="shared" si="32"/>
+        <v>1791213787.94165</v>
+      </c>
+      <c r="E93" s="77"/>
+      <c r="F93" s="77">
+        <f t="shared" si="33"/>
+        <v>9361452.75469378</v>
+      </c>
+      <c r="G93" s="79"/>
+      <c r="P93" s="98"/>
+      <c r="Q93" s="109"/>
+      <c r="R93" s="109"/>
+      <c r="S93" s="109"/>
+      <c r="T93" s="107"/>
+    </row>
+    <row r="94" ht="15.75" customHeight="1" spans="2:7">
+      <c r="B94" s="65">
+        <f t="shared" si="34"/>
         <v>245483.333333333</v>
       </c>
-      <c r="C91" s="75">
-        <f t="shared" si="47"/>
-        <v>231798.673462895</v>
-      </c>
-      <c r="D91" s="75">
-        <f t="shared" si="48"/>
-        <v>187269915.769574</v>
-      </c>
-      <c r="E91" s="75">
-        <f t="shared" si="49"/>
-        <v>122669226.254233</v>
-      </c>
-      <c r="F91" s="77"/>
-    </row>
-    <row r="92" ht="15.75" customHeight="1" spans="2:6">
-      <c r="B92" s="53">
-        <f t="shared" si="50"/>
+      <c r="C94" s="77">
+        <f t="shared" si="31"/>
+        <v>195604.84371406</v>
+      </c>
+      <c r="D94" s="77">
+        <f t="shared" si="32"/>
+        <v>2487863726.69995</v>
+      </c>
+      <c r="E94" s="77"/>
+      <c r="F94" s="77">
+        <f t="shared" si="33"/>
+        <v>120479508.31025</v>
+      </c>
+      <c r="G94" s="79"/>
+    </row>
+    <row r="95" ht="15.75" customHeight="1" spans="2:7">
+      <c r="B95" s="65">
+        <f t="shared" si="34"/>
         <v>251530</v>
       </c>
-      <c r="C92" s="75">
-        <f t="shared" si="47"/>
-        <v>228454.457289466</v>
-      </c>
-      <c r="D92" s="75">
-        <f t="shared" si="48"/>
-        <v>532480671.385668</v>
-      </c>
-      <c r="E92" s="75">
-        <f t="shared" si="49"/>
-        <v>293172496.429672</v>
-      </c>
-      <c r="F92" s="77"/>
-    </row>
-    <row r="93" ht="15.75" customHeight="1" spans="1:13">
-      <c r="A93" s="78"/>
-      <c r="B93" s="53">
-        <f t="shared" si="50"/>
+      <c r="C95" s="77">
+        <f t="shared" si="31"/>
+        <v>215388.815248438</v>
+      </c>
+      <c r="D95" s="77">
+        <f t="shared" si="32"/>
+        <v>1306185235.24653</v>
+      </c>
+      <c r="E95" s="77"/>
+      <c r="F95" s="77">
+        <f t="shared" si="33"/>
+        <v>289781931.702063</v>
+      </c>
+      <c r="G95" s="79"/>
+    </row>
+    <row r="96" ht="15.75" customHeight="1" spans="1:16">
+      <c r="A96" s="80"/>
+      <c r="B96" s="65">
+        <f t="shared" si="34"/>
         <v>257510</v>
       </c>
-      <c r="C93" s="75">
-        <f t="shared" si="47"/>
-        <v>226067.759329802</v>
-      </c>
-      <c r="D93" s="75">
-        <f t="shared" si="48"/>
-        <v>988614498.362633</v>
-      </c>
-      <c r="E93" s="75">
-        <f t="shared" si="49"/>
-        <v>533715373.622654</v>
-      </c>
-      <c r="F93" s="77"/>
-      <c r="M93" s="105"/>
-    </row>
-    <row r="94" ht="15.75" customHeight="1" spans="1:13">
-      <c r="A94" s="79"/>
-      <c r="B94" s="53">
-        <f t="shared" si="50"/>
+      <c r="C96" s="77">
+        <f t="shared" si="31"/>
+        <v>247925.823870938</v>
+      </c>
+      <c r="D96" s="77">
+        <f t="shared" si="32"/>
+        <v>91856432.0728861</v>
+      </c>
+      <c r="E96" s="77"/>
+      <c r="F96" s="77">
+        <f t="shared" si="33"/>
+        <v>529137201.877501</v>
+      </c>
+      <c r="G96" s="79"/>
+      <c r="P96" s="99"/>
+    </row>
+    <row r="97" ht="15.75" customHeight="1" spans="1:16">
+      <c r="A97" s="81"/>
+      <c r="B97" s="65">
+        <f t="shared" si="34"/>
         <v>259583.333333333</v>
       </c>
-      <c r="C94" s="75">
-        <f t="shared" si="47"/>
-        <v>223217.300778364</v>
-      </c>
-      <c r="D94" s="75">
-        <f t="shared" si="48"/>
-        <v>1322488323.7891</v>
-      </c>
-      <c r="E94" s="75">
-        <f t="shared" si="49"/>
-        <v>633811542.043707</v>
-      </c>
-      <c r="F94" s="77"/>
-      <c r="M94" s="106"/>
-    </row>
-    <row r="95" ht="15.75" customHeight="1" spans="2:13">
-      <c r="B95" s="53">
-        <f t="shared" si="50"/>
+      <c r="C97" s="77">
+        <f t="shared" si="31"/>
+        <v>283566.547487802</v>
+      </c>
+      <c r="D97" s="77">
+        <f t="shared" si="32"/>
+        <v>575194561.179128</v>
+      </c>
+      <c r="E97" s="77"/>
+      <c r="F97" s="77">
+        <f t="shared" si="33"/>
+        <v>628821613.573408</v>
+      </c>
+      <c r="G97" s="79"/>
+      <c r="P97" s="100"/>
+    </row>
+    <row r="98" ht="15.75" customHeight="1" spans="2:16">
+      <c r="B98" s="65">
+        <f t="shared" si="34"/>
         <v>264456.666666667</v>
       </c>
-      <c r="C95" s="75">
-        <f t="shared" si="47"/>
-        <v>224566.233536435</v>
-      </c>
-      <c r="D95" s="75">
-        <f t="shared" si="48"/>
-        <v>1591246655.31752</v>
-      </c>
-      <c r="E95" s="75">
-        <f t="shared" si="49"/>
-        <v>902939237.950141</v>
-      </c>
-      <c r="F95" s="77"/>
-      <c r="M95" s="107"/>
-    </row>
-    <row r="96" ht="15.75" customHeight="1" spans="2:13">
-      <c r="B96" s="53">
-        <f t="shared" si="50"/>
+      <c r="C98" s="77">
+        <f t="shared" si="31"/>
+        <v>298170.578479842</v>
+      </c>
+      <c r="D98" s="77">
+        <f t="shared" si="32"/>
+        <v>1136627849.74654</v>
+      </c>
+      <c r="E98" s="77"/>
+      <c r="F98" s="77">
+        <f t="shared" si="33"/>
+        <v>896981482.579257</v>
+      </c>
+      <c r="G98" s="79"/>
+      <c r="P98" s="101"/>
+    </row>
+    <row r="99" ht="15.75" customHeight="1" spans="2:16">
+      <c r="B99" s="65">
+        <f t="shared" si="34"/>
         <v>270176.666666667</v>
       </c>
-      <c r="C96" s="75">
-        <f t="shared" si="47"/>
-        <v>224566.233536435</v>
-      </c>
-      <c r="D96" s="75">
-        <f t="shared" si="48"/>
-        <v>2080311610.32738</v>
-      </c>
-      <c r="E96" s="75">
-        <f t="shared" si="49"/>
-        <v>1279417595.84488</v>
-      </c>
-      <c r="F96" s="77"/>
-      <c r="M96" s="107"/>
-    </row>
-    <row r="97" ht="15.75" customHeight="1" spans="2:13">
-      <c r="B97" s="53">
-        <f t="shared" si="50"/>
+      <c r="C99" s="77">
+        <f t="shared" si="31"/>
+        <v>298170.578479842</v>
+      </c>
+      <c r="D99" s="77">
+        <f t="shared" si="32"/>
+        <v>783659098.603816</v>
+      </c>
+      <c r="E99" s="77"/>
+      <c r="F99" s="77">
+        <f t="shared" si="33"/>
+        <v>1272323868.54417</v>
+      </c>
+      <c r="G99" s="79"/>
+      <c r="P99" s="101"/>
+    </row>
+    <row r="100" ht="15.75" customHeight="1" spans="2:16">
+      <c r="B100" s="65">
+        <f t="shared" si="34"/>
         <v>276430</v>
       </c>
-      <c r="C97" s="75">
-        <f t="shared" si="47"/>
-        <v>226496.39464437</v>
-      </c>
-      <c r="D97" s="75">
-        <f t="shared" si="48"/>
-        <v>2493364943.81177</v>
-      </c>
-      <c r="E97" s="75">
-        <f t="shared" si="49"/>
-        <v>1765872075.37704</v>
-      </c>
-      <c r="F97" s="77"/>
-      <c r="M97" s="107"/>
-    </row>
-    <row r="98" ht="15.75" customHeight="1" spans="2:13">
-      <c r="B98" s="53">
-        <f t="shared" si="50"/>
+      <c r="C100" s="77">
+        <f t="shared" si="31"/>
+        <v>286981.434910395</v>
+      </c>
+      <c r="D100" s="77">
+        <f t="shared" si="32"/>
+        <v>111332778.668296</v>
+      </c>
+      <c r="E100" s="77"/>
+      <c r="F100" s="77">
+        <f t="shared" si="33"/>
+        <v>1757536458.01785</v>
+      </c>
+      <c r="G100" s="79"/>
+      <c r="P100" s="101"/>
+    </row>
+    <row r="101" ht="15.75" customHeight="1" spans="2:16">
+      <c r="B101" s="65">
+        <f t="shared" si="34"/>
         <v>282813.333333333</v>
       </c>
-      <c r="C98" s="75">
-        <f t="shared" si="47"/>
-        <v>234494.570842006</v>
-      </c>
-      <c r="D98" s="75">
-        <f t="shared" si="48"/>
-        <v>2334702808.69331</v>
-      </c>
-      <c r="E98" s="75">
-        <f t="shared" si="49"/>
-        <v>2343103470.11388</v>
-      </c>
-      <c r="F98" s="77"/>
-      <c r="M98" s="107"/>
-    </row>
-    <row r="99" ht="15.75" customHeight="1" spans="2:13">
-      <c r="B99" s="80">
-        <f t="shared" si="50"/>
+      <c r="C101" s="77">
+        <f t="shared" si="31"/>
+        <v>286358.937549181</v>
+      </c>
+      <c r="D101" s="77">
+        <f t="shared" si="32"/>
+        <v>12571309.2554356</v>
+      </c>
+      <c r="E101" s="77"/>
+      <c r="F101" s="77">
+        <f t="shared" si="33"/>
+        <v>2333500145.15235</v>
+      </c>
+      <c r="G101" s="79"/>
+      <c r="P101" s="101"/>
+    </row>
+    <row r="102" ht="15.75" customHeight="1" spans="2:16">
+      <c r="B102" s="82">
+        <f t="shared" si="34"/>
         <v>285890</v>
       </c>
-      <c r="C99" s="81">
-        <f t="shared" si="47"/>
-        <v>242413.604576209</v>
-      </c>
-      <c r="D99" s="81">
-        <f t="shared" si="48"/>
-        <v>1890196959.0458</v>
-      </c>
-      <c r="E99" s="81">
-        <f t="shared" si="49"/>
-        <v>2650425226.25423</v>
-      </c>
-      <c r="F99" s="77"/>
-      <c r="M99" s="107"/>
-    </row>
-    <row r="100" ht="15.75" customHeight="1" spans="2:13">
-      <c r="B100" s="82">
-        <f t="shared" si="50"/>
-        <v>287850</v>
-      </c>
-      <c r="C100" s="83">
-        <f t="shared" si="47"/>
-        <v>248483.514252609</v>
-      </c>
-      <c r="D100" s="83">
-        <f t="shared" si="48"/>
-        <v>1549720200.09956</v>
-      </c>
-      <c r="E100" s="83">
-        <f t="shared" si="49"/>
-        <v>2856077366.60511</v>
-      </c>
-      <c r="F100" s="77"/>
-      <c r="M100" s="107"/>
-    </row>
-    <row r="101" ht="15.75" customHeight="1" spans="6:13">
-      <c r="F101" s="77"/>
-      <c r="M101" s="107"/>
-    </row>
-    <row r="102" ht="15.75" customHeight="1" spans="6:13">
-      <c r="F102" s="77"/>
-      <c r="M102" s="107"/>
-    </row>
-    <row r="103" ht="15.75" customHeight="1" spans="6:13">
-      <c r="F103" s="77"/>
-      <c r="M103" s="107"/>
-    </row>
-    <row r="104" ht="15.75" customHeight="1" spans="6:13">
-      <c r="F104" s="77"/>
-      <c r="M104" s="107"/>
-    </row>
-    <row r="105" ht="15.75" customHeight="1" spans="2:13">
-      <c r="B105" s="84" t="s">
-        <v>69</v>
-      </c>
-      <c r="F105" s="77"/>
-      <c r="M105" s="107"/>
-    </row>
-    <row r="106" ht="15.75" customHeight="1" spans="2:13">
-      <c r="B106" s="82">
-        <f>AVERAGE(B82:B100)</f>
-        <v>234407.719298246</v>
-      </c>
-      <c r="C106" s="85"/>
-      <c r="F106" s="77"/>
-      <c r="M106" s="107"/>
-    </row>
-    <row r="107" ht="15.75" customHeight="1" spans="2:5">
-      <c r="B107" s="84" t="s">
-        <v>70</v>
-      </c>
-      <c r="C107" s="86"/>
-      <c r="D107" s="86"/>
-      <c r="E107" s="86"/>
-    </row>
-    <row r="108" ht="15.75" customHeight="1" spans="2:5">
-      <c r="B108" s="82">
-        <f>SQRT(1-(SUM(D82:D100)/SUM(E82:E100)))</f>
-        <v>0.469930221644802</v>
-      </c>
-      <c r="C108" s="86"/>
-      <c r="D108" s="86"/>
-      <c r="E108" s="86"/>
-    </row>
-    <row r="109" ht="15.75" customHeight="1" spans="2:5">
-      <c r="B109" s="87"/>
-      <c r="C109" s="86"/>
-      <c r="D109" s="86"/>
-      <c r="E109" s="86"/>
-    </row>
-    <row r="110" ht="15.75" customHeight="1"/>
-    <row r="111" ht="15.75" customHeight="1"/>
-    <row r="112" ht="15.75" customHeight="1"/>
-    <row r="113" ht="15.75" customHeight="1" spans="2:4">
-      <c r="B113" s="88" t="s">
-        <v>71</v>
-      </c>
-      <c r="C113" s="27"/>
-      <c r="D113" s="34"/>
-    </row>
+      <c r="C102" s="83">
+        <f t="shared" si="31"/>
+        <v>287133.435797127</v>
+      </c>
+      <c r="D102" s="83">
+        <f t="shared" si="32"/>
+        <v>1546132.58157778</v>
+      </c>
+      <c r="E102" s="83"/>
+      <c r="F102" s="83">
+        <f t="shared" si="33"/>
+        <v>2640210886.08803</v>
+      </c>
+      <c r="G102" s="79"/>
+      <c r="P102" s="101"/>
+    </row>
+    <row r="103" ht="15.75" customHeight="1" spans="2:16">
+      <c r="B103" s="84">
+        <f t="shared" si="34"/>
+        <v>289736.666666667</v>
+      </c>
+      <c r="C103" s="85">
+        <f t="shared" si="31"/>
+        <v>293238.619703872</v>
+      </c>
+      <c r="D103" s="85">
+        <f t="shared" si="32"/>
+        <v>12263675.0747937</v>
+      </c>
+      <c r="E103" s="85"/>
+      <c r="F103" s="85">
+        <f t="shared" si="33"/>
+        <v>3050314142.22838</v>
+      </c>
+      <c r="G103" s="79"/>
+      <c r="P103" s="101"/>
+    </row>
+    <row r="104" ht="15.75" customHeight="1" spans="7:16">
+      <c r="G104" s="79"/>
+      <c r="P104" s="101"/>
+    </row>
+    <row r="105" ht="15.75" customHeight="1" spans="7:16">
+      <c r="G105" s="79"/>
+      <c r="P105" s="101"/>
+    </row>
+    <row r="106" ht="15.75" customHeight="1" spans="7:16">
+      <c r="G106" s="79"/>
+      <c r="P106" s="101"/>
+    </row>
+    <row r="107" ht="15.75" customHeight="1" spans="7:16">
+      <c r="G107" s="79"/>
+      <c r="P107" s="101"/>
+    </row>
+    <row r="108" ht="15.75" customHeight="1" spans="2:16">
+      <c r="B108" s="86" t="s">
+        <v>77</v>
+      </c>
+      <c r="G108" s="79"/>
+      <c r="P108" s="101"/>
+    </row>
+    <row r="109" ht="15.75" customHeight="1" spans="2:16">
+      <c r="B109" s="84">
+        <f>AVERAGE(B85:B103)</f>
+        <v>234507.01754386</v>
+      </c>
+      <c r="C109" s="25"/>
+      <c r="G109" s="79"/>
+      <c r="P109" s="101"/>
+    </row>
+    <row r="110" ht="15.75" customHeight="1" spans="2:6">
+      <c r="B110" s="86" t="s">
+        <v>78</v>
+      </c>
+      <c r="C110" s="87"/>
+      <c r="D110" s="87"/>
+      <c r="E110" s="87"/>
+      <c r="F110" s="87"/>
+    </row>
+    <row r="111" ht="15.75" customHeight="1" spans="2:6">
+      <c r="B111" s="84">
+        <f>SQRT(1-(SUM(D85:D103)/SUM(F85:F103)))</f>
+        <v>0.813463091592422</v>
+      </c>
+      <c r="C111" s="87"/>
+      <c r="D111" s="87"/>
+      <c r="E111" s="87"/>
+      <c r="F111" s="87"/>
+    </row>
+    <row r="112" ht="15.75" customHeight="1" spans="2:6">
+      <c r="B112" s="88"/>
+      <c r="C112" s="87"/>
+      <c r="D112" s="87"/>
+      <c r="E112" s="87"/>
+      <c r="F112" s="87"/>
+    </row>
+    <row r="113" ht="15.75" customHeight="1"/>
     <row r="114" ht="15.75" customHeight="1"/>
-    <row r="115" ht="15.75" customHeight="1" spans="2:13">
-      <c r="B115" s="77"/>
-      <c r="C115" s="77"/>
-      <c r="D115" s="77"/>
-      <c r="E115" s="77"/>
-      <c r="F115" s="77"/>
-      <c r="G115" s="55"/>
-      <c r="M115" s="107"/>
-    </row>
-    <row r="116" ht="15.75" customHeight="1" spans="2:13">
-      <c r="B116" s="89"/>
-      <c r="C116" s="90"/>
+    <row r="115" ht="15.75" customHeight="1"/>
+    <row r="116" ht="15.75" customHeight="1" spans="2:4">
+      <c r="B116" s="89" t="s">
+        <v>79</v>
+      </c>
+      <c r="C116" s="24"/>
       <c r="D116" s="90"/>
-      <c r="E116" s="90"/>
-      <c r="F116" s="91"/>
-      <c r="G116" s="92"/>
-      <c r="H116" s="85"/>
-      <c r="I116" s="85"/>
-      <c r="J116" s="85"/>
-      <c r="K116" s="108"/>
-      <c r="L116" s="109"/>
-      <c r="M116" s="110"/>
-    </row>
-    <row r="117" ht="15.75" customHeight="1" spans="2:13">
-      <c r="B117" s="93"/>
-      <c r="C117" s="94"/>
-      <c r="D117" s="94"/>
-      <c r="E117" s="94"/>
-      <c r="F117" s="95"/>
-      <c r="G117" s="96"/>
-      <c r="H117" s="97"/>
-      <c r="I117" s="97"/>
-      <c r="J117" s="97"/>
-      <c r="K117" s="108"/>
-      <c r="L117" s="109"/>
-      <c r="M117" s="110"/>
-    </row>
-    <row r="118" ht="15.75" customHeight="1" spans="2:13">
-      <c r="B118" s="98" t="s">
-        <v>72</v>
-      </c>
-      <c r="C118" s="98" t="s">
-        <v>73</v>
-      </c>
-      <c r="D118" s="98" t="s">
-        <v>74</v>
-      </c>
-      <c r="E118" s="77" t="s">
-        <v>75</v>
-      </c>
-      <c r="H118" s="85"/>
-      <c r="I118" s="85"/>
-      <c r="J118" s="85"/>
-      <c r="K118" s="108"/>
-      <c r="L118" s="109"/>
-      <c r="M118" s="110"/>
-    </row>
-    <row r="119" ht="15.75" customHeight="1" spans="2:13">
-      <c r="B119" s="53">
-        <f>B106</f>
-        <v>234407.719298246</v>
-      </c>
-      <c r="C119" s="53">
-        <f>AVERAGE(I6:I27)</f>
-        <v>27419.7368421053</v>
-      </c>
-      <c r="D119" s="53">
-        <f>AVERAGE(G6:G27)</f>
-        <v>268.210526315789</v>
-      </c>
-      <c r="E119" s="77" t="s">
-        <v>76</v>
-      </c>
-      <c r="M119" s="107"/>
-    </row>
-    <row r="120" ht="15.75" customHeight="1" spans="1:13">
-      <c r="A120" s="25"/>
-      <c r="B120" s="89"/>
-      <c r="C120" s="90"/>
-      <c r="D120" s="90"/>
-      <c r="E120" s="90"/>
-      <c r="F120" s="90"/>
-      <c r="G120" s="90"/>
-      <c r="H120" s="90"/>
-      <c r="I120" s="91"/>
-      <c r="J120" s="111"/>
-      <c r="K120" s="112"/>
-      <c r="L120" s="112"/>
-      <c r="M120" s="110"/>
-    </row>
-    <row r="121" ht="15.75" customHeight="1" spans="1:13">
-      <c r="A121" s="28"/>
-      <c r="B121" s="93"/>
-      <c r="C121" s="94"/>
-      <c r="D121" s="94"/>
-      <c r="E121" s="94"/>
-      <c r="F121" s="94"/>
-      <c r="G121" s="94"/>
-      <c r="H121" s="94"/>
-      <c r="I121" s="95"/>
-      <c r="J121" s="113"/>
-      <c r="K121" s="114"/>
-      <c r="L121" s="114"/>
-      <c r="M121" s="106"/>
-    </row>
-    <row r="122" ht="15.75" customHeight="1" spans="1:6">
-      <c r="A122" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B122" s="99">
-        <f>F78*(B119/D119)</f>
-        <v>315.380158260167</v>
-      </c>
-      <c r="C122" s="100" t="s">
-        <v>78</v>
-      </c>
-      <c r="D122" s="101" t="s">
-        <v>79</v>
-      </c>
-      <c r="E122" s="101"/>
-      <c r="F122" s="101"/>
-    </row>
-    <row r="123" ht="15.75" customHeight="1" spans="1:6">
-      <c r="A123" s="1" t="s">
+    </row>
+    <row r="117" ht="15.75" customHeight="1"/>
+    <row r="118" ht="15.75" customHeight="1" spans="2:16">
+      <c r="B118" s="79"/>
+      <c r="C118" s="79"/>
+      <c r="D118" s="79"/>
+      <c r="E118" s="79"/>
+      <c r="F118" s="79"/>
+      <c r="G118" s="79"/>
+      <c r="H118" s="67"/>
+      <c r="P118" s="101"/>
+    </row>
+    <row r="119" ht="15.75" customHeight="1" spans="2:16">
+      <c r="B119" s="91"/>
+      <c r="C119" s="91"/>
+      <c r="D119" s="91"/>
+      <c r="E119" s="91"/>
+      <c r="F119" s="91"/>
+      <c r="G119" s="91"/>
+      <c r="H119" s="92"/>
+      <c r="I119" s="25"/>
+      <c r="J119" s="25"/>
+      <c r="K119" s="25"/>
+      <c r="L119" s="25"/>
+      <c r="M119" s="102"/>
+      <c r="N119" s="102"/>
+      <c r="O119" s="103"/>
+      <c r="P119" s="104"/>
+    </row>
+    <row r="120" ht="15.75" customHeight="1" spans="2:16">
+      <c r="B120" s="91"/>
+      <c r="C120" s="91"/>
+      <c r="D120" s="91"/>
+      <c r="E120" s="91"/>
+      <c r="F120" s="91"/>
+      <c r="G120" s="91"/>
+      <c r="H120" s="92"/>
+      <c r="I120" s="25"/>
+      <c r="J120" s="25"/>
+      <c r="K120" s="25"/>
+      <c r="L120" s="25"/>
+      <c r="M120" s="102"/>
+      <c r="N120" s="102"/>
+      <c r="O120" s="103"/>
+      <c r="P120" s="104"/>
+    </row>
+    <row r="121" ht="15.75" customHeight="1" spans="2:16">
+      <c r="B121" s="93" t="s">
         <v>80</v>
       </c>
-      <c r="B123" s="99">
-        <f>F77*(B119/C119)</f>
-        <v>8.62731468361788</v>
-      </c>
-      <c r="C123" s="100" t="s">
-        <v>78</v>
-      </c>
-      <c r="D123" s="101" t="s">
+      <c r="C121" s="93" t="s">
         <v>81</v>
       </c>
-      <c r="E123" s="101"/>
-      <c r="F123" s="101"/>
-    </row>
-    <row r="124" ht="15.75" customHeight="1" spans="4:4">
-      <c r="D124" s="84"/>
-    </row>
-    <row r="125" ht="15.75" customHeight="1" spans="1:1">
-      <c r="A125" s="102"/>
-    </row>
-    <row r="126" ht="15.75" customHeight="1" spans="1:1">
-      <c r="A126" s="103"/>
-    </row>
-    <row r="127" ht="15.75" customHeight="1"/>
-    <row r="128" ht="15.75" customHeight="1" spans="2:3">
-      <c r="B128" s="84"/>
-      <c r="C128" s="99"/>
-    </row>
-    <row r="129" ht="15.75" customHeight="1" spans="2:4">
-      <c r="B129" s="115" t="s">
+      <c r="D121" s="93" t="s">
         <v>82</v>
       </c>
-      <c r="D129" s="116">
-        <f>F78</f>
-        <v>0.360859610296757</v>
-      </c>
+      <c r="E121" s="79"/>
+      <c r="F121" s="79" t="s">
+        <v>83</v>
+      </c>
+      <c r="I121" s="25"/>
+      <c r="J121" s="25"/>
+      <c r="K121" s="25"/>
+      <c r="L121" s="25"/>
+      <c r="M121" s="102"/>
+      <c r="N121" s="102"/>
+      <c r="O121" s="103"/>
+      <c r="P121" s="104"/>
+    </row>
+    <row r="122" ht="15.75" customHeight="1" spans="2:16">
+      <c r="B122" s="65">
+        <f>B109</f>
+        <v>234507.01754386</v>
+      </c>
+      <c r="C122" s="65">
+        <f>AVERAGE(J6:J30)</f>
+        <v>27907.9545454545</v>
+      </c>
+      <c r="D122" s="65">
+        <f>AVERAGE(H6:H30)</f>
+        <v>286.636363636364</v>
+      </c>
+      <c r="E122" s="79"/>
+      <c r="F122" s="79" t="s">
+        <v>84</v>
+      </c>
+      <c r="P122" s="101"/>
+    </row>
+    <row r="123" ht="15.75" customHeight="1" spans="1:16">
+      <c r="A123" s="22"/>
+      <c r="B123" s="91"/>
+      <c r="C123" s="91"/>
+      <c r="D123" s="91"/>
+      <c r="E123" s="91"/>
+      <c r="F123" s="91"/>
+      <c r="G123" s="91"/>
+      <c r="H123" s="91"/>
+      <c r="I123" s="91"/>
+      <c r="J123" s="91"/>
+      <c r="K123" s="97"/>
+      <c r="L123" s="97"/>
+      <c r="M123" s="97"/>
+      <c r="N123" s="97"/>
+      <c r="O123" s="105"/>
+      <c r="P123" s="104"/>
+    </row>
+    <row r="124" ht="15.75" customHeight="1" spans="1:16">
+      <c r="A124" s="18"/>
+      <c r="B124" s="91"/>
+      <c r="C124" s="91"/>
+      <c r="D124" s="91"/>
+      <c r="E124" s="91"/>
+      <c r="F124" s="91"/>
+      <c r="G124" s="91"/>
+      <c r="H124" s="91"/>
+      <c r="I124" s="91"/>
+      <c r="J124" s="91"/>
+      <c r="K124" s="97"/>
+      <c r="L124" s="97"/>
+      <c r="M124" s="97"/>
+      <c r="N124" s="97"/>
+      <c r="O124" s="106"/>
+      <c r="P124" s="100"/>
+    </row>
+    <row r="125" ht="15.75" customHeight="1" spans="1:7">
+      <c r="A125" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B125" s="94">
+        <f>G81*(B122/D122)</f>
+        <v>-1319.42452246666</v>
+      </c>
+      <c r="C125" s="95" t="s">
+        <v>86</v>
+      </c>
+      <c r="D125" s="96" t="s">
+        <v>87</v>
+      </c>
+      <c r="E125" s="96"/>
+      <c r="F125" s="96"/>
+      <c r="G125" s="96"/>
+    </row>
+    <row r="126" ht="15.75" customHeight="1" spans="1:7">
+      <c r="A126" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B126" s="94">
+        <f>G80*(B122/C122)</f>
+        <v>70.6819588699601</v>
+      </c>
+      <c r="C126" s="95" t="s">
+        <v>89</v>
+      </c>
+      <c r="D126" s="96" t="s">
+        <v>90</v>
+      </c>
+      <c r="E126" s="96"/>
+      <c r="F126" s="96"/>
+      <c r="G126" s="96"/>
+    </row>
+    <row r="127" ht="15.75" customHeight="1" spans="4:4">
+      <c r="D127" s="86"/>
+    </row>
+    <row r="128" ht="15.75" customHeight="1" spans="1:1">
+      <c r="A128" s="22"/>
+    </row>
+    <row r="129" ht="15.75" customHeight="1" spans="1:1">
+      <c r="A129" s="18"/>
     </row>
     <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1" spans="2:5">
-      <c r="B131" s="117" t="s">
-        <v>83</v>
-      </c>
-      <c r="C131" s="118"/>
-      <c r="D131" s="118"/>
-      <c r="E131" s="118"/>
-    </row>
-    <row r="132" ht="15.75" customHeight="1" spans="2:5">
-      <c r="B132" s="117" t="s">
-        <v>84</v>
-      </c>
-      <c r="C132" s="85"/>
-      <c r="D132" s="85"/>
-      <c r="E132" s="85"/>
-    </row>
-    <row r="133" ht="15.75" customHeight="1" spans="2:5">
-      <c r="B133" s="119" t="s">
-        <v>85</v>
-      </c>
-      <c r="C133" s="120"/>
-      <c r="D133" s="120"/>
-      <c r="E133" s="120"/>
-    </row>
-    <row r="134" ht="15.75" customHeight="1" spans="2:4">
-      <c r="B134" s="121"/>
-      <c r="C134" s="122"/>
-      <c r="D134" s="122"/>
-    </row>
-    <row r="135" ht="15.75" customHeight="1" spans="2:2">
-      <c r="B135" s="123" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1" spans="2:6">
-      <c r="B137" s="115" t="s">
-        <v>87</v>
-      </c>
-      <c r="D137" s="116">
-        <f>F77</f>
-        <v>1.0091762292941</v>
-      </c>
-      <c r="F137" s="118"/>
-    </row>
-    <row r="138" ht="15.75" customHeight="1" spans="6:6">
-      <c r="F138" s="85"/>
-    </row>
-    <row r="139" ht="15.75" customHeight="1" spans="2:6">
-      <c r="B139" s="124" t="s">
-        <v>88</v>
-      </c>
-      <c r="C139" s="125"/>
-      <c r="D139" s="125"/>
-      <c r="E139" s="125"/>
-      <c r="F139" s="120"/>
-    </row>
-    <row r="140" ht="15.75" customHeight="1" spans="2:12">
-      <c r="B140" s="117" t="s">
-        <v>89</v>
-      </c>
-      <c r="C140" s="85"/>
-      <c r="D140" s="85"/>
-      <c r="E140" s="85"/>
-      <c r="F140" s="126"/>
-      <c r="G140" s="126"/>
-      <c r="H140" s="126"/>
-      <c r="I140" s="52"/>
-      <c r="J140" s="52"/>
-      <c r="K140" s="52"/>
-      <c r="L140" s="64"/>
-    </row>
-    <row r="141" ht="15.75" customHeight="1" spans="2:8">
-      <c r="B141" s="117" t="s">
-        <v>90</v>
-      </c>
-      <c r="C141" s="118"/>
-      <c r="D141" s="118"/>
-      <c r="E141" s="118"/>
-      <c r="F141" s="29"/>
-      <c r="G141" s="29"/>
-      <c r="H141" s="29"/>
-    </row>
-    <row r="142" ht="15.75" customHeight="1" spans="2:8">
-      <c r="B142" s="29"/>
-      <c r="C142" s="29"/>
-      <c r="D142" s="29"/>
-      <c r="E142" s="29"/>
-      <c r="F142" s="29"/>
-      <c r="G142" s="29"/>
-      <c r="H142" s="29"/>
-    </row>
-    <row r="143" ht="15.75" customHeight="1" spans="2:8">
-      <c r="B143" s="127"/>
-      <c r="E143" s="29"/>
-      <c r="F143" s="29"/>
-      <c r="G143" s="29"/>
-      <c r="H143" s="29"/>
-    </row>
-    <row r="144" ht="15.75" customHeight="1" spans="2:8">
-      <c r="B144" s="128"/>
-      <c r="C144" s="126"/>
-      <c r="D144" s="126"/>
-      <c r="E144" s="126"/>
-      <c r="F144" s="126"/>
-      <c r="G144" s="126"/>
-      <c r="H144" s="126"/>
-    </row>
-    <row r="145" ht="15.75" customHeight="1" spans="6:8">
-      <c r="F145" s="125"/>
-      <c r="G145" s="129"/>
-      <c r="H145" s="130"/>
-    </row>
-    <row r="146" ht="15.75" customHeight="1" spans="6:8">
-      <c r="F146" s="85"/>
-      <c r="G146" s="29"/>
-      <c r="H146" s="131"/>
-    </row>
-    <row r="147" ht="15.75" customHeight="1" spans="6:8">
-      <c r="F147" s="118"/>
-      <c r="G147" s="29"/>
-      <c r="H147" s="132"/>
-    </row>
-    <row r="148" ht="15.75" customHeight="1" spans="2:8">
-      <c r="B148" s="85"/>
-      <c r="C148" s="85"/>
-      <c r="D148" s="85"/>
-      <c r="E148" s="85"/>
-      <c r="F148" s="85"/>
-      <c r="G148" s="29"/>
-      <c r="H148" s="133"/>
-    </row>
-    <row r="149" ht="15.75" customHeight="1" spans="3:8">
-      <c r="C149" s="85"/>
-      <c r="D149" s="85"/>
-      <c r="E149" s="85"/>
-      <c r="F149" s="85"/>
-      <c r="G149" s="29"/>
-      <c r="H149" s="133"/>
-    </row>
-    <row r="150" ht="15.75" customHeight="1" spans="2:8">
-      <c r="B150" s="134"/>
-      <c r="C150" s="134"/>
-      <c r="D150" s="134"/>
-      <c r="E150" s="134"/>
-      <c r="F150" s="134"/>
-      <c r="G150" s="29"/>
-      <c r="H150" s="133"/>
-    </row>
-    <row r="151" ht="15.75" customHeight="1" spans="2:8">
-      <c r="B151" s="134"/>
-      <c r="C151" s="134"/>
-      <c r="D151" s="134"/>
-      <c r="E151" s="134"/>
-      <c r="F151" s="134"/>
-      <c r="G151" s="29"/>
-      <c r="H151" s="133"/>
-    </row>
-    <row r="152" ht="15.75" customHeight="1" spans="2:8">
-      <c r="B152" s="134"/>
-      <c r="C152" s="134"/>
-      <c r="D152" s="134"/>
-      <c r="E152" s="134"/>
-      <c r="F152" s="134"/>
-      <c r="G152" s="29"/>
-      <c r="H152" s="133"/>
-    </row>
-    <row r="153" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A153" s="102"/>
-      <c r="B153" s="134"/>
-      <c r="C153" s="134"/>
-      <c r="D153" s="134"/>
-      <c r="E153" s="134"/>
-      <c r="F153" s="134"/>
-      <c r="G153" s="135"/>
-      <c r="H153" s="133"/>
-    </row>
-    <row r="154" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A154" s="103"/>
-      <c r="B154" s="134"/>
-      <c r="C154" s="134"/>
-      <c r="D154" s="134"/>
-      <c r="E154" s="134"/>
-      <c r="F154" s="134"/>
-      <c r="G154" s="136"/>
-      <c r="H154" s="133"/>
-    </row>
-    <row r="155" ht="15.75" customHeight="1" spans="2:8">
-      <c r="B155" s="134"/>
-      <c r="C155" s="134"/>
-      <c r="D155" s="134"/>
-      <c r="E155" s="134"/>
-      <c r="F155" s="134"/>
-      <c r="G155" s="137"/>
-      <c r="H155" s="133"/>
-    </row>
-    <row r="156" ht="15.75" customHeight="1" spans="7:8">
-      <c r="G156" s="29"/>
-      <c r="H156" s="133"/>
-    </row>
-    <row r="157" ht="15.75" customHeight="1" spans="7:8">
-      <c r="G157" s="29"/>
-      <c r="H157" s="133"/>
-    </row>
-    <row r="158" ht="15.75" customHeight="1" spans="7:8">
-      <c r="G158" s="29"/>
-      <c r="H158" s="133"/>
-    </row>
-    <row r="159" ht="15.75" customHeight="1" spans="7:8">
-      <c r="G159" s="29"/>
-      <c r="H159" s="133"/>
-    </row>
-    <row r="160" ht="15.75" customHeight="1" spans="7:8">
-      <c r="G160" s="29"/>
-      <c r="H160" s="133"/>
-    </row>
-    <row r="161" ht="15.75" customHeight="1" spans="7:8">
-      <c r="G161" s="135"/>
-      <c r="H161" s="133"/>
-    </row>
-    <row r="162" ht="15.75" customHeight="1" spans="7:8">
-      <c r="G162" s="136"/>
-      <c r="H162" s="133"/>
-    </row>
-    <row r="163" ht="15.75" customHeight="1" spans="7:8">
-      <c r="G163" s="137"/>
-      <c r="H163" s="133"/>
-    </row>
-    <row r="164" ht="15.75" customHeight="1" spans="7:8">
-      <c r="G164" s="29"/>
-      <c r="H164" s="133"/>
-    </row>
-    <row r="165" ht="15.75" customHeight="1" spans="7:8">
-      <c r="G165" s="29"/>
-      <c r="H165" s="133"/>
-    </row>
-    <row r="166" ht="15.75" customHeight="1" spans="7:8">
-      <c r="G166" s="29"/>
-      <c r="H166" s="133"/>
-    </row>
-    <row r="167" ht="15.75" customHeight="1" spans="7:8">
-      <c r="G167" s="29"/>
-      <c r="H167" s="133"/>
-    </row>
-    <row r="168" ht="15.75" customHeight="1" spans="7:8">
-      <c r="G168" s="29"/>
-      <c r="H168" s="133"/>
-    </row>
-    <row r="169" ht="15.75" customHeight="1" spans="7:8">
-      <c r="G169" s="29"/>
-      <c r="H169" s="133"/>
-    </row>
-    <row r="170" ht="15.75" customHeight="1" spans="7:8">
-      <c r="G170" s="29"/>
-      <c r="H170" s="133"/>
-    </row>
-    <row r="171" ht="15.75" customHeight="1" spans="7:8">
-      <c r="G171" s="29"/>
-      <c r="H171" s="133"/>
-    </row>
-    <row r="172" ht="15.75" customHeight="1" spans="7:8">
-      <c r="G172" s="29"/>
-      <c r="H172" s="133"/>
-    </row>
-    <row r="173" ht="15.75" customHeight="1" spans="2:8">
-      <c r="B173" s="65"/>
-      <c r="C173" s="52"/>
-      <c r="D173" s="52"/>
-      <c r="E173" s="52"/>
-      <c r="F173" s="52"/>
-      <c r="G173" s="52"/>
-      <c r="H173" s="64"/>
-    </row>
-    <row r="174" ht="15.75" customHeight="1" spans="7:8">
-      <c r="G174" s="29"/>
-      <c r="H174" s="29"/>
-    </row>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1" spans="2:3">
+      <c r="B131" s="86"/>
+      <c r="C131" s="94"/>
+    </row>
+    <row r="132" ht="15.75" customHeight="1" spans="2:4">
+      <c r="B132" s="110" t="s">
+        <v>91</v>
+      </c>
+      <c r="D132" s="111">
+        <f>G81</f>
+        <v>-1.61272379468028</v>
+      </c>
+    </row>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1" spans="2:6">
+      <c r="B134" s="25" t="s">
+        <v>92</v>
+      </c>
+      <c r="C134" s="97"/>
+      <c r="D134" s="97"/>
+      <c r="E134" s="97"/>
+      <c r="F134" s="97"/>
+    </row>
+    <row r="135" ht="15.75" customHeight="1" spans="2:6">
+      <c r="B135" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="C135" s="25"/>
+      <c r="D135" s="25"/>
+      <c r="E135" s="25"/>
+      <c r="F135" s="25"/>
+    </row>
+    <row r="136" ht="15.75" customHeight="1" spans="2:6">
+      <c r="B136" s="25"/>
+      <c r="C136" s="97"/>
+      <c r="D136" s="97"/>
+      <c r="E136" s="97"/>
+      <c r="F136" s="97"/>
+    </row>
+    <row r="137" ht="15.75" customHeight="1" spans="2:4">
+      <c r="B137" s="112"/>
+      <c r="C137" s="113"/>
+      <c r="D137" s="113"/>
+    </row>
+    <row r="138" ht="15.75" customHeight="1" spans="2:2">
+      <c r="B138" s="114" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1" spans="2:7">
+      <c r="B140" s="110" t="s">
+        <v>95</v>
+      </c>
+      <c r="D140" s="111">
+        <f>G80</f>
+        <v>8.4116412207477</v>
+      </c>
+      <c r="G140" s="97"/>
+    </row>
+    <row r="141" ht="15.75" customHeight="1" spans="7:7">
+      <c r="G141" s="25"/>
+    </row>
+    <row r="142" ht="15.75" customHeight="1" spans="2:7">
+      <c r="B142" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="C142" s="97"/>
+      <c r="D142" s="97"/>
+      <c r="E142" s="97"/>
+      <c r="F142" s="97"/>
+      <c r="G142" s="97"/>
+    </row>
+    <row r="143" ht="15.75" customHeight="1" spans="2:15">
+      <c r="B143" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="C143" s="25"/>
+      <c r="D143" s="25"/>
+      <c r="E143" s="25"/>
+      <c r="F143" s="25"/>
+      <c r="G143" s="25"/>
+      <c r="H143" s="25"/>
+      <c r="I143" s="25"/>
+      <c r="J143" s="97"/>
+      <c r="K143" s="97"/>
+      <c r="L143" s="97"/>
+      <c r="M143" s="97"/>
+      <c r="N143" s="97"/>
+      <c r="O143" s="117"/>
+    </row>
+    <row r="144" ht="15.75" customHeight="1" spans="2:9">
+      <c r="B144" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="C144" s="97"/>
+      <c r="D144" s="97"/>
+      <c r="E144" s="97"/>
+      <c r="F144" s="97"/>
+      <c r="G144" s="25"/>
+      <c r="H144" s="25"/>
+      <c r="I144" s="25"/>
+    </row>
+    <row r="145" ht="15.75" customHeight="1" spans="2:9">
+      <c r="B145" s="25"/>
+      <c r="C145" s="25"/>
+      <c r="D145" s="25"/>
+      <c r="E145" s="25"/>
+      <c r="F145" s="25"/>
+      <c r="G145" s="25"/>
+      <c r="H145" s="25"/>
+      <c r="I145" s="25"/>
+    </row>
+    <row r="146" ht="15.75" customHeight="1" spans="2:9">
+      <c r="B146" s="115"/>
+      <c r="F146" s="25"/>
+      <c r="G146" s="25"/>
+      <c r="H146" s="25"/>
+      <c r="I146" s="25"/>
+    </row>
+    <row r="147" ht="15.75" customHeight="1" spans="2:9">
+      <c r="B147" s="92"/>
+      <c r="C147" s="25"/>
+      <c r="D147" s="25"/>
+      <c r="E147" s="25"/>
+      <c r="F147" s="25"/>
+      <c r="G147" s="25"/>
+      <c r="H147" s="25"/>
+      <c r="I147" s="25"/>
+    </row>
+    <row r="148" ht="15.75" customHeight="1" spans="7:9">
+      <c r="G148" s="97"/>
+      <c r="H148" s="91"/>
+      <c r="I148" s="91"/>
+    </row>
+    <row r="149" ht="15.75" customHeight="1" spans="7:9">
+      <c r="G149" s="25"/>
+      <c r="H149" s="25"/>
+      <c r="I149" s="102"/>
+    </row>
+    <row r="150" ht="15.75" customHeight="1" spans="7:9">
+      <c r="G150" s="97"/>
+      <c r="H150" s="25"/>
+      <c r="I150" s="25"/>
+    </row>
+    <row r="151" ht="15.75" customHeight="1" spans="2:9">
+      <c r="B151" s="25"/>
+      <c r="C151" s="25"/>
+      <c r="D151" s="25"/>
+      <c r="E151" s="25"/>
+      <c r="F151" s="25"/>
+      <c r="G151" s="25"/>
+      <c r="H151" s="25"/>
+      <c r="I151" s="97"/>
+    </row>
+    <row r="152" ht="15.75" customHeight="1" spans="3:9">
+      <c r="C152" s="25"/>
+      <c r="D152" s="25"/>
+      <c r="E152" s="25"/>
+      <c r="F152" s="25"/>
+      <c r="G152" s="25"/>
+      <c r="H152" s="25"/>
+      <c r="I152" s="97"/>
+    </row>
+    <row r="153" ht="15.75" customHeight="1" spans="2:9">
+      <c r="B153" s="116"/>
+      <c r="C153" s="116"/>
+      <c r="D153" s="116"/>
+      <c r="E153" s="116"/>
+      <c r="F153" s="116"/>
+      <c r="G153" s="116"/>
+      <c r="H153" s="25"/>
+      <c r="I153" s="97"/>
+    </row>
+    <row r="154" ht="15.75" customHeight="1" spans="2:9">
+      <c r="B154" s="116"/>
+      <c r="C154" s="116"/>
+      <c r="D154" s="116"/>
+      <c r="E154" s="116"/>
+      <c r="F154" s="116"/>
+      <c r="G154" s="116"/>
+      <c r="H154" s="25"/>
+      <c r="I154" s="97"/>
+    </row>
+    <row r="155" ht="15.75" customHeight="1" spans="2:9">
+      <c r="B155" s="116"/>
+      <c r="C155" s="116"/>
+      <c r="D155" s="116"/>
+      <c r="E155" s="116"/>
+      <c r="F155" s="116"/>
+      <c r="G155" s="116"/>
+      <c r="H155" s="25"/>
+      <c r="I155" s="97"/>
+    </row>
+    <row r="156" ht="15.75" customHeight="1" spans="1:9">
+      <c r="A156" s="22"/>
+      <c r="B156" s="116"/>
+      <c r="C156" s="116"/>
+      <c r="D156" s="116"/>
+      <c r="E156" s="116"/>
+      <c r="F156" s="116"/>
+      <c r="G156" s="116"/>
+      <c r="H156" s="97"/>
+      <c r="I156" s="97"/>
+    </row>
+    <row r="157" ht="15.75" customHeight="1" spans="1:9">
+      <c r="A157" s="18"/>
+      <c r="B157" s="116"/>
+      <c r="C157" s="116"/>
+      <c r="D157" s="116"/>
+      <c r="E157" s="116"/>
+      <c r="F157" s="116"/>
+      <c r="G157" s="116"/>
+      <c r="H157" s="97"/>
+      <c r="I157" s="97"/>
+    </row>
+    <row r="158" ht="15.75" customHeight="1" spans="2:9">
+      <c r="B158" s="116"/>
+      <c r="C158" s="116"/>
+      <c r="D158" s="116"/>
+      <c r="E158" s="116"/>
+      <c r="F158" s="116"/>
+      <c r="G158" s="116"/>
+      <c r="H158" s="97"/>
+      <c r="I158" s="97"/>
+    </row>
+    <row r="159" ht="15.75" customHeight="1" spans="8:9">
+      <c r="H159" s="25"/>
+      <c r="I159" s="97"/>
+    </row>
+    <row r="160" ht="15.75" customHeight="1" spans="8:9">
+      <c r="H160" s="25"/>
+      <c r="I160" s="97"/>
+    </row>
+    <row r="161" ht="15.75" customHeight="1" spans="8:9">
+      <c r="H161" s="25"/>
+      <c r="I161" s="97"/>
+    </row>
+    <row r="162" ht="15.75" customHeight="1" spans="8:9">
+      <c r="H162" s="25"/>
+      <c r="I162" s="97"/>
+    </row>
+    <row r="163" ht="15.75" customHeight="1" spans="8:9">
+      <c r="H163" s="25"/>
+      <c r="I163" s="97"/>
+    </row>
+    <row r="164" ht="15.75" customHeight="1" spans="8:9">
+      <c r="H164" s="97"/>
+      <c r="I164" s="97"/>
+    </row>
+    <row r="165" ht="15.75" customHeight="1" spans="8:9">
+      <c r="H165" s="97"/>
+      <c r="I165" s="97"/>
+    </row>
+    <row r="166" ht="15.75" customHeight="1" spans="8:9">
+      <c r="H166" s="97"/>
+      <c r="I166" s="97"/>
+    </row>
+    <row r="167" ht="15.75" customHeight="1" spans="8:9">
+      <c r="H167" s="25"/>
+      <c r="I167" s="97"/>
+    </row>
+    <row r="168" ht="15.75" customHeight="1" spans="8:9">
+      <c r="H168" s="25"/>
+      <c r="I168" s="97"/>
+    </row>
+    <row r="169" ht="15.75" customHeight="1" spans="8:9">
+      <c r="H169" s="25"/>
+      <c r="I169" s="97"/>
+    </row>
+    <row r="170" ht="15.75" customHeight="1" spans="8:9">
+      <c r="H170" s="25"/>
+      <c r="I170" s="97"/>
+    </row>
+    <row r="171" ht="15.75" customHeight="1" spans="8:9">
+      <c r="H171" s="25"/>
+      <c r="I171" s="97"/>
+    </row>
+    <row r="172" ht="15.75" customHeight="1" spans="8:9">
+      <c r="H172" s="25"/>
+      <c r="I172" s="97"/>
+    </row>
+    <row r="173" ht="15.75" customHeight="1" spans="8:9">
+      <c r="H173" s="25"/>
+      <c r="I173" s="97"/>
+    </row>
+    <row r="174" ht="15.75" customHeight="1" spans="8:9">
+      <c r="H174" s="25"/>
+      <c r="I174" s="97"/>
+    </row>
+    <row r="175" ht="15.75" customHeight="1" spans="8:9">
+      <c r="H175" s="25"/>
+      <c r="I175" s="97"/>
+    </row>
+    <row r="176" ht="15.75" customHeight="1" spans="2:9">
+      <c r="B176" s="30"/>
+      <c r="C176" s="97"/>
+      <c r="D176" s="97"/>
+      <c r="E176" s="97"/>
+      <c r="F176" s="97"/>
+      <c r="G176" s="97"/>
+      <c r="H176" s="97"/>
+      <c r="I176" s="97"/>
+    </row>
+    <row r="177" ht="15.75" customHeight="1" spans="8:9">
+      <c r="H177" s="25"/>
+      <c r="I177" s="25"/>
+    </row>
     <row r="178" ht="15.75" customHeight="1"/>
     <row r="179" ht="15.75" customHeight="1"/>
     <row r="180" ht="15.75" customHeight="1"/>
@@ -6661,31 +7676,32 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
+    <row r="1002" ht="15.75" customHeight="1"/>
+    <row r="1003" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="23">
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="B26:I26"/>
-    <mergeCell ref="J28:Q28"/>
-    <mergeCell ref="B29:I29"/>
-    <mergeCell ref="B34:J34"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B113:D113"/>
-    <mergeCell ref="E118:G118"/>
-    <mergeCell ref="E119:G119"/>
-    <mergeCell ref="D122:F122"/>
-    <mergeCell ref="D123:F123"/>
-    <mergeCell ref="A29:A30"/>
+  <mergeCells count="21">
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="H3:K3"/>
+    <mergeCell ref="B29:J29"/>
+    <mergeCell ref="B32:J32"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B116:D116"/>
+    <mergeCell ref="F121:H121"/>
+    <mergeCell ref="F122:H122"/>
+    <mergeCell ref="D125:G125"/>
+    <mergeCell ref="D126:G126"/>
     <mergeCell ref="A32:A33"/>
-    <mergeCell ref="A63:A64"/>
-    <mergeCell ref="A89:A90"/>
-    <mergeCell ref="A93:A94"/>
-    <mergeCell ref="A120:A121"/>
-    <mergeCell ref="A125:A126"/>
-    <mergeCell ref="A153:A154"/>
-    <mergeCell ref="I30:I31"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="Q2:Q3"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="A123:A124"/>
+    <mergeCell ref="A128:A129"/>
+    <mergeCell ref="A156:A157"/>
+    <mergeCell ref="J33:J34"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="U2:U3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="1" orientation="landscape"/>
